--- a/leads_psicologo_curitiba.xlsx
+++ b/leads_psicologo_curitiba.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N53"/>
+  <dimension ref="A1:N44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,12 +491,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Google Maps</t>
+          <t>20 psiclogos</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Google Maps</t>
+          <t>20 psicólogos em Curitiba para apoio emocional</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -511,34 +511,34 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Explore Google Maps for Street View, 3D mapping, turn-by-turn directions, indoor maps and more on yo...</t>
+          <t>Se você está buscando psicólogos em Curitiba, aqui você encontra profissionais preparados para te at...</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SEM SITE (OPORTUNIDADE QUENTE 🔥)</t>
+          <t>SITE ATIVO 📱</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sem Site Cadastrado</t>
+          <t>https://mindee.com.br/psicologos/curitiba-pr</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
+          <t>(CU) 98877-6655</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Google%20Maps%20curitiba</t>
+          <t>https://www.google.com/maps/search/20%20psiclogos%20curitiba</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Google Maps aí em Curitiba no Google e vi que vocês ainda não têm um site próprio para celular.
+Vi o perfil da 20 psiclogos aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -548,29 +548,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Google Maps?</t>
+Posso te mandar a prévia demonstrativa que fiz para a 20 psiclogos?</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Google%20Maps%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%2020%20psiclogos%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Google%20Maps%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%2020%20psiclogos%3F</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Psicloga online / Psicloga Curitiba</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Psicóloga online / Psicóloga Curitiba - Psicóloga Amanda Amarante</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -585,34 +585,34 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Google...</t>
+          <t>A Psicoterapeuta Amanda Amarante. psicologa curitiba. Olá, sou a Amanda. Psicóloga, formada pela PUC...</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SEM SITE (OPORTUNIDADE QUENTE 🔥)</t>
+          <t>SITE ATIVO 📱</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sem Site Cadastrado</t>
+          <t>https://www.psicologaamandaamarante.com.br/</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
+          <t>(CU) 98877-6655</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Google%20curitiba</t>
+          <t>https://www.google.com/maps/search/Psicloga%20online%20/%20Psicloga%20Curitiba%20curitiba</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Google aí em Curitiba no Google e vi que vocês ainda não têm um site próprio para celular.
+Vi o perfil da Psicloga online / Psicloga Curitiba aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -622,29 +622,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Google?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Psicloga online / Psicloga Curitiba?</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Google%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Psicloga%20online%20/%20Psicloga%20Curitiba%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Google%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Psicloga%20online%20/%20Psicloga%20Curitiba%3F</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20 psiclogos</t>
+          <t>psicologo</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>20 psicólogos em Curitiba para apoio emocional</t>
+          <t>psicologo em Curitiba/PR — 1787 profissionais — Velora</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Se você está buscando psicólogos em Curitiba, aqui você encontra profissionais preparados para te at...</t>
+          <t>psicologo em Curitiba. 1787 profissionais encontrados em Curitiba/PR. Não sabe qual escolher? A Piet...</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -669,24 +669,28 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://mindee.com.br/psicologos/curitiba-pr</t>
+          <t>https://velora.tech/pr/curitiba/psicologo/</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(41) 99644-0186</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5541996440186</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/20%20psiclogos%20curitiba</t>
+          <t>https://www.google.com/maps/search/psicologo%20curitiba</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da 20 psiclogos aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da psicologo aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -696,29 +700,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a 20 psiclogos?</t>
+Posso te mandar a prévia demonstrativa que fiz para a psicologo?</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=20%20psiclogos%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541996440186?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20psicologo%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=20%20psiclogos%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541996440186?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20psicologo%3F</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Yandex Maps: search for places, transport, an</t>
+          <t>AutoRank para Psiclogos</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Yandex Maps: search for places, transport, and routes</t>
+          <t>AutoRank para Psicólogos em Curitiba | Seu Consultório na Primeir</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -733,7 +737,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Yandex Maps will help you find your destination even if you don't have the exact address — get a rou...</t>
+          <t>Psicólogos em Curitiba. Pacientes buscando psicólogo, terapia, ansiedade e depressão te encontram no...</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -743,24 +747,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://yandex.com/maps/</t>
+          <t>https://www.autorank.com.br/psicologo/curitiba</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
+          <t>(CU) 98877-6655</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Yandex%20Maps%3A%20search%20for%20places%2C%20transport%2C%20an%20curitiba</t>
+          <t>https://www.google.com/maps/search/AutoRank%20para%20Psiclogos%20curitiba</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Yandex Maps: search for places, transport, an aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da AutoRank para Psiclogos aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -770,29 +774,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Yandex Maps: search for places, transport, an?</t>
+Posso te mandar a prévia demonstrativa que fiz para a AutoRank para Psiclogos?</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Yandex%20Maps%3A%20search%20for%20places%2C%20transport%2C%20an%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20AutoRank%20para%20Psiclogos%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Yandex%20Maps%3A%20search%20for%20places%2C%20transport%2C%20an%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20AutoRank%20para%20Psiclogos%3F</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Psicloga online / Psicloga Curitiba</t>
+          <t>Psiclogos, Clnicas de Psicologia na Cidade de</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Psicóloga online / Psicóloga Curitiba - Psicóloga Amanda Amarante</t>
+          <t>Psicólogos, Clínicas de Psicologia na Cidade de Curitiba - Paraná</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -807,7 +811,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>A Psicoterapeuta Amanda Amarante. psicologa curitiba. Olá, sou a Amanda. Psicóloga, formada pela PUC...</t>
+          <t>psicologo curitiba gratuito. clinica de psicologia em curitiba.psicologo curitiba amil. psicólogas e...</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -817,24 +821,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.psicologaamandaamarante.com.br/</t>
+          <t>https://www.encontracuritiba.com.br/p/psicologa-em-curitiba.shtml</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
+          <t>(CU) 98877-6655</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Psicloga%20online%20/%20Psicloga%20Curitiba%20curitiba</t>
+          <t>https://www.google.com/maps/search/Psiclogos%2C%20Clnicas%20de%20Psicologia%20na%20Cidade%20de%20curitiba</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Psicloga online / Psicloga Curitiba aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Psiclogos, Clnicas de Psicologia na Cidade de aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -844,29 +848,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Psicloga online / Psicloga Curitiba?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Psiclogos, Clnicas de Psicologia na Cidade de?</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Psicloga%20online%20/%20Psicloga%20Curitiba%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Psiclogos%2C%20Clnicas%20de%20Psicologia%20na%20Cidade%20de%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Psicloga%20online%20/%20Psicloga%20Curitiba%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Psiclogos%2C%20Clnicas%20de%20Psicologia%20na%20Cidade%20de%3F</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AutoRank para Psiclogos</t>
+          <t>Psiclogos Curitiba</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AutoRank para Psicólogos em Curitiba | Seu Consultório na Primeir</t>
+          <t>Psicólogos Curitiba - MundoPsicologos.com - br</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -881,7 +885,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Psicólogos em Curitiba. Pacientes buscando psicólogo, terapia, ansiedade e depressão te encontram no...</t>
+          <t>Aqui você encontra informações sobre centros e clínica de Psicologia, e pode entram em contato com p...</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -891,24 +895,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.autorank.com.br/psicologo/curitiba</t>
+          <t>https://br.mundopsicologos.com/consultorios/curitiba</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
+          <t>(CU) 98877-6655</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/AutoRank%20para%20Psiclogos%20curitiba</t>
+          <t>https://www.google.com/maps/search/Psiclogos%20Curitiba%20curitiba</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da AutoRank para Psiclogos aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Psiclogos Curitiba aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -918,29 +922,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a AutoRank para Psiclogos?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Psiclogos Curitiba?</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=AutoRank%20para%20Psiclogos%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Psiclogos%20Curitiba%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=AutoRank%20para%20Psiclogos%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Psiclogos%20Curitiba%3F</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10 melhores psiclogos para Curitiba</t>
+          <t>Psicologias / Psiclogos</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10 melhores psicólogos para Curitiba</t>
+          <t>Psicologias / Psicólogos em Curitiba, PR — WhatsApp</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -955,34 +959,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nossos melhores psicólogos em Curitiba, avaliados pela comunidade StarOfService - Curitiba, Paraná.P...</t>
+          <t>Veja os psicólogos mais bem avaliados em Curitiba, PR. Terapia individual, de casal, infantil, avali...</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SITE ATIVO 📱</t>
+          <t>SEM SITE (OPORTUNIDADE QUENTE 🔥)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.starofservice.com.br/dir/parana/curitiba/curitiba/psicologia</t>
+          <t>Sem Site Cadastrado</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
+          <t>(CU) 98877-6655</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/10%20melhores%20psiclogos%20para%20Curitiba%20curitiba</t>
+          <t>https://www.google.com/maps/search/Psicologias%20/%20Psiclogos%20curitiba</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da 10 melhores psiclogos para Curitiba aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Psicologias / Psiclogos aí em Curitiba no Google e vi que vocês ainda não têm um site próprio para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -992,29 +996,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a 10 melhores psiclogos para Curitiba?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Psicologias / Psiclogos?</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=10%20melhores%20psiclogos%20para%20Curitiba%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Psicologias%20/%20Psiclogos%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20voc%C3%AAs%20ainda%20n%C3%A3o%20t%C3%AAm%20um%20site%20pr%C3%B3prio%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=10%20melhores%20psiclogos%20para%20Curitiba%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Psicologias%20/%20Psiclogos%3F</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Em busca de um psiclogo</t>
+          <t>Psicloga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Em busca de um psicólogo em Curitiba? Consulte os convênios...</t>
+          <t>Psicóloga em Curitiba | Psicoterapia Online | Isabela Cazé</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1029,7 +1033,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Conectamos você ao psicólogo ideal para seu objetivo. Consulta presencial e online. Esclareça suas d...</t>
+          <t>Atendimento presencial em Curitiba e online para adolescentes, adultos, casais e famílias, com enfoq...</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1039,24 +1043,28 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://psicologo.curitiba.br/</t>
+          <t>https://isabelacazepsicologa.com/</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(11) 98723-2712</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5511987232712</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Em%20busca%20de%20um%20psiclogo%20curitiba</t>
+          <t>https://www.google.com/maps/search/Psicloga%20curitiba</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Em busca de um psiclogo aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Psicloga aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1066,29 +1074,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Em busca de um psiclogo?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Psicloga?</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Em%20busca%20de%20um%20psiclogo%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5511987232712?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Psicloga%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Em%20busca%20de%20um%20psiclogo%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5511987232712?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Psicloga%3F</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Psiclogos</t>
+          <t>Psiclogos, Curitiba, PR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Psicólogos em Curitiba: Ache o melhor | Agende sua consulta com..</t>
+          <t>Psicólogos, Curitiba, PR - Central Terapia</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1103,7 +1111,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ache o melhor Psicólogos com avaliações, preços dos serviços, anos de experiência em Curitiba e agen...</t>
+          <t>Psicólogos perto de você! Obtenha suporte e consulta especializada com os mais recomendados psicólog...</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1113,24 +1121,28 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.doctoranytime.com.br/s/psicologo/curitiba</t>
+          <t>https://centralterapia.com.br/psicologo/curitiba-pr/</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>41999756</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5541999756</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Psiclogos%20curitiba</t>
+          <t>https://www.google.com/maps/search/Psiclogos%2C%20Curitiba%2C%20PR%20curitiba</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Psiclogos aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Psiclogos, Curitiba, PR aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1140,29 +1152,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Psiclogos?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Psiclogos, Curitiba, PR?</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Psiclogos%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541999756?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Psiclogos%2C%20Curitiba%2C%20PR%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Psiclogos%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541999756?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Psiclogos%2C%20Curitiba%2C%20PR%3F</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Psiclogos Curitiba</t>
+          <t>Leonardo Fd Araujo</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Psicólogos Curitiba - MundoPsicologos.com - br</t>
+          <t>Leonardo Fd Araujo | Psicólogo em Curitiba | Bigorrilho</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1177,7 +1189,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aqui você encontra informações sobre centros e clínica de Psicologia, e pode entram em contato com p...</t>
+          <t>Psicólogo em Curitiba, com experiência em psicoterapia, avaliação psicológica, elaboração de laudos ...</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1187,28 +1199,28 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://br.mundopsicologos.com/consultorios/curitiba</t>
+          <t>https://psicologoemcuritiba.com.br/</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5541999756</t>
+          <t>(41) 99643-9560</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>554199975600</t>
+          <t>5541996439560</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Psiclogos%20Curitiba%20curitiba</t>
+          <t>https://www.google.com/maps/search/Leonardo%20Fd%20Araujo%20curitiba</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Psiclogos Curitiba aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Leonardo Fd Araujo aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1218,29 +1230,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Psiclogos Curitiba?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Leonardo Fd Araujo?</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://wa.me/554199975600?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Psiclogos%20Curitiba%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541996439560?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Leonardo%20Fd%20Araujo%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>https://wa.me/554199975600?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Psiclogos%20Curitiba%3F</t>
+          <t>https://wa.me/5541996439560?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Leonardo%20Fd%20Araujo%3F</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Stelmach Psicologia</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Stelmach Psicologia | Gestalt-Terapia e Psicanálise</t>
+          <t>ITC - Instituto Terapêutico de Curitiba — psicologo em Curitiba/P</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1255,7 +1267,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Psicólogo clínico com especialização em estresse, doenças psicossomáticas e autoimunes. Grupos de de...</t>
+          <t>Resposta rápida pelo WhatsApp. A ITC - Instituto Terapêutico de Curitiba oferece atendimento com psi...</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1265,24 +1277,28 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.stelmach.psc.br/</t>
+          <t>https://velora.tech/pr/curitiba/psicologo/itc-instituto-terapeutico-de-curitiba-288248</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>41301914</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5541301914</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Stelmach%20Psicologia%20curitiba</t>
+          <t>https://www.google.com/maps/search/ITC%20curitiba</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Stelmach Psicologia aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da ITC aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1292,29 +1308,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Stelmach Psicologia?</t>
+Posso te mandar a prévia demonstrativa que fiz para a ITC?</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Stelmach%20Psicologia%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541301914?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20ITC%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Stelmach%20Psicologia%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541301914?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20ITC%3F</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Psicologo</t>
+          <t>104 avaliaes sobre Psicloga Infantil</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Psicologo | Curitiba | PsicoEliPassos</t>
+          <t>104 avaliações sobre Psicóloga Infantil | Especialista em Curitib</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1329,34 +1345,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Artigos. Blog | PsicoEliPassos | Curitiba. Contato....</t>
+          <t>Situada em Curitiba (Paraná). Clique e confira as informações e comentários.A dra. é muito atenciosa...</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SITE FORA DO AR (ERRO 404) 🚨</t>
+          <t>SITE ATIVO 📱</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.psicoelipassos.com.br/</t>
+          <t>https://avaliacoesbrasil.com/psicologo/curitiba/psicologa-infantil-especialist/</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(41) 3585-1481</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>554135851481</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Psicologo%20curitiba</t>
+          <t>https://www.google.com/maps/search/104%20avaliaes%20sobre%20Psicloga%20Infantil%20curitiba</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Psicologo aí em Curitiba no Google e fui tentar acessar o site de vocês e vi que está fora do ar.
+Vi o perfil da 104 avaliaes sobre Psicloga Infantil aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1366,29 +1386,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Psicologo?</t>
+Posso te mandar a prévia demonstrativa que fiz para a 104 avaliaes sobre Psicloga Infantil?</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Psicologo%20curitiba%20whatsapp</t>
+          <t>https://wa.me/554135851481?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20104%20avaliaes%20sobre%20Psicloga%20Infantil%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Psicologo%20curitiba%20whatsapp</t>
+          <t>https://wa.me/554135851481?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20104%20avaliaes%20sobre%20Psicloga%20Infantil%3F</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Psicologo Bueno Junior</t>
+          <t>Hudson Padilha • Psiclogo Curitiba. Psicanali</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Psicologo Bueno Junior</t>
+          <t>Hudson Padilha • Psicólogo Curitiba. Psicanalista ...</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1403,7 +1423,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sou psicólogo em Curitiba, com mais de 20 anos de experiência em atendimentos presenciais e online. ...</t>
+          <t>Hudson é Psicanalista e Psicólogo (CRP:08/36638) com especialização em Psicanálise: Sujeito e Cultur...</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1413,24 +1433,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://psicologobuenojr.com.br/</t>
+          <t>https://www.hudsonpadilha.com/</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
+          <t>(CU) 98877-6655</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Psicologo%20Bueno%20Junior%20curitiba</t>
+          <t>https://www.google.com/maps/search/Hudson%20Padilha%20%E2%80%A2%20Psiclogo%20Curitiba.%20Psicanali%20curitiba</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Psicologo Bueno Junior aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Hudson Padilha • Psiclogo Curitiba. Psicanali aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1440,29 +1460,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Psicologo Bueno Junior?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Hudson Padilha • Psiclogo Curitiba. Psicanali?</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Psicologo%20Bueno%20Junior%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Hudson%20Padilha%20%E2%80%A2%20Psiclogo%20Curitiba.%20Psicanali%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Psicologo%20Bueno%20Junior%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Hudson%20Padilha%20%E2%80%A2%20Psiclogo%20Curitiba.%20Psicanali%3F</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>Link to facebook.com</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ITC - Instituto Terapêutico de Curitiba — psicologo em Curitiba/P</t>
+          <t>Link to facebook.com</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1477,34 +1497,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Resposta rápida pelo WhatsApp. A ITC - Instituto Terapêutico de Curitiba oferece atendimento com psi...</t>
+          <t>The site owner hides the web page description....</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SITE ATIVO 📱</t>
+          <t>SEM SITE PRÓPRIO (OPORTUNIDADE 🔥)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://velora.tech/pr/curitiba/psicologo/itc-instituto-terapeutico-de-curitiba-288248</t>
+          <t>Sem Site Cadastrado</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
+          <t>(CU) 98877-6655</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/ITC%20curitiba</t>
+          <t>https://www.google.com/maps/search/Link%20to%20facebook.com%20curitiba</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da ITC aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Link to facebook.com aí em Curitiba no Google e vi que vocês ainda não têm um site próprio para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1514,29 +1534,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a ITC?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Link to facebook.com?</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=ITC%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Link%20to%20facebook.com%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20voc%C3%AAs%20ainda%20n%C3%A3o%20t%C3%AAm%20um%20site%20pr%C3%B3prio%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=ITC%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Link%20to%20facebook.com%3F</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Psiclogo, Curitiba, PR</t>
+          <t>20 melhores Psicanalistas e Psiclogos de Curi</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Psicólogo, Curitiba, PR - Rede Psicólogos</t>
+          <t>20 melhores Psicanalistas e Psicólogos de Curitiba - Psicanálise.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1551,7 +1571,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Curitiba. Procurando um Psicólogo(a) perto de você?Envie um WhatsApp diretamente para a(o) psicóloga...</t>
+          <t>15 melhores Psicólogos de Curitiba para você e sua família.O Dr. Pedro Elias Sater atende na clínica...</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1561,24 +1581,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://redepsicologos.com.br/psicologo/curitiba/</t>
+          <t>https://www.psicanaliseclinica.com/psicologos-de-curitiba/</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
+          <t>(CU) 98877-6655</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Psiclogo%2C%20Curitiba%2C%20PR%20curitiba</t>
+          <t>https://www.google.com/maps/search/20%20melhores%20Psicanalistas%20e%20Psiclogos%20de%20Curi%20curitiba</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Psiclogo, Curitiba, PR aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da 20 melhores Psicanalistas e Psiclogos de Curi aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1588,29 +1608,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Psiclogo, Curitiba, PR?</t>
+Posso te mandar a prévia demonstrativa que fiz para a 20 melhores Psicanalistas e Psiclogos de Curi?</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Psiclogo%2C%20Curitiba%2C%20PR%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%2020%20melhores%20Psicanalistas%20e%20Psiclogos%20de%20Curi%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Psiclogo%2C%20Curitiba%2C%20PR%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%2020%20melhores%20Psicanalistas%20e%20Psiclogos%20de%20Curi%3F</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Psicologo Curitiba Jorge Luiz Hipnoterapia Co</t>
+          <t>Rael Psiclogo</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Psicologo Curitiba Jorge Luiz Hipnoterapia Consultorio de...</t>
+          <t>Rael Psicólogo - Curitiba Centro PR - Telefone... | Bendito Guia</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1625,7 +1645,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Clique em "Contato" para nos fazer uma chamada. Você nos localiza no endereço , no bairro em Curitib...</t>
+          <t>Encontre o telefone, endereço e whatsapp de Rael Psicólogo - Curitiba Centro PR em Atibaia. Veja ava...</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1635,28 +1655,28 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://guiafacil.com/site/psicologo-curitiba-jorge-luiz-hipnoterapia-consultorio-de-psicologia-ansiedade-fobias-vicios-depress/curitiba/pr/3577782</t>
+          <t>https://www.benditoguia.com.br/empresa/rael-psicologo-curitiba-centro-pr</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>47 99164-1987</t>
+          <t>(41) 99600-4058</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>554799164198700</t>
+          <t>5541996004058</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Psicologo%20Curitiba%20Jorge%20Luiz%20Hipnoterapia%20Co%20curitiba</t>
+          <t>https://www.google.com/maps/search/Rael%20Psiclogo%20curitiba</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Psicologo Curitiba Jorge Luiz Hipnoterapia Co aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Rael Psiclogo aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1666,29 +1686,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Psicologo Curitiba Jorge Luiz Hipnoterapia Co?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Rael Psiclogo?</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>https://wa.me/554799164198700?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Psicologo%20Curitiba%20Jorge%20Luiz%20Hipnoterapia%20Co%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541996004058?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Rael%20Psiclogo%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>https://wa.me/554799164198700?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Psicologo%20Curitiba%20Jorge%20Luiz%20Hipnoterapia%20Co%3F</t>
+          <t>https://wa.me/5541996004058?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Rael%20Psiclogo%3F</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Link to facebook.com</t>
+          <t>63 avaliaes sobre Clnica</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Link to facebook.com</t>
+          <t>63 avaliações sobre Clínica em Curitiba - Clínica Reintegrar...</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1703,38 +1723,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>The site owner hides the web page description....</t>
+          <t>Avaliações » Psicologo » Paraná » Curitiba » Clinica reintegrar.Mapa. Horário de funcionamento de Cl...</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SEM SITE (OPORTUNIDADE QUENTE 🔥)</t>
+          <t>SITE ATIVO 📱</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sem Site Cadastrado</t>
+          <t>https://avaliacoesbrasil.com/psicologo/curitiba/clinica-reintegrar/</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>41 98420-4581</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>554198420458100</t>
-        </is>
-      </c>
+          <t>(CU) 98877-6655</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Link%20to%20facebook.com%20curitiba</t>
+          <t>https://www.google.com/maps/search/63%20avaliaes%20sobre%20Clnica%20curitiba</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Link to facebook.com aí em Curitiba no Google e vi que vocês ainda não têm um site próprio para celular.
+Vi o perfil da 63 avaliaes sobre Clnica aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1744,29 +1760,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Link to facebook.com?</t>
+Posso te mandar a prévia demonstrativa que fiz para a 63 avaliaes sobre Clnica?</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>https://wa.me/554198420458100?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Link%20to%20facebook.com%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20voc%C3%AAs%20ainda%20n%C3%A3o%20t%C3%AAm%20um%20site%20pr%C3%B3prio%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%2063%20avaliaes%20sobre%20Clnica%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>https://wa.me/554198420458100?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Link%20to%20facebook.com%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%2063%20avaliaes%20sobre%20Clnica%3F</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Psiclogos, Clnicas de Psicologia na Cidade de</t>
+          <t>Psiclogo Gratuito</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Psicólogos, Clínicas de Psicologia na Cidade de Curitiba - Paraná</t>
+          <t>Psicólogo Gratuito em Curitiba - Psicólogo gratuito, Psicólogo...</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1781,7 +1797,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>psicologo curitiba gratuito. clinica de psicologia em curitiba.psicologo curitiba amil. psicólogas e...</t>
+          <t>Psicólogo Gratuito em Curitiba. Buscar apoio psicológico é um passo importante para o bem-estar.Tele...</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1791,24 +1807,28 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.encontracuritiba.com.br/p/psicologa-em-curitiba.shtml</t>
+          <t>https://psicologogratuito.com.br/psicologo-gratuito-em-curitiba/</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(41) 3310-1515</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>554133101515</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Psiclogos%2C%20Clnicas%20de%20Psicologia%20na%20Cidade%20de%20curitiba</t>
+          <t>https://www.google.com/maps/search/Psiclogo%20Gratuito%20curitiba</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Psiclogos, Clnicas de Psicologia na Cidade de aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Psiclogo Gratuito aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1818,29 +1838,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Psiclogos, Clnicas de Psicologia na Cidade de?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Psiclogo Gratuito?</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Psiclogos%2C%20Clnicas%20de%20Psicologia%20na%20Cidade%20de%20curitiba%20whatsapp</t>
+          <t>https://wa.me/554133101515?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Psiclogo%20Gratuito%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Psiclogos%2C%20Clnicas%20de%20Psicologia%20na%20Cidade%20de%20curitiba%20whatsapp</t>
+          <t>https://wa.me/554133101515?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Psiclogo%20Gratuito%3F</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20 melhores Psicanalistas e Psiclogos de Curi</t>
+          <t>Sabina Arajo Dos Santos Fagundes, Psiclogo</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>20 melhores Psicanalistas e Psicólogos de Curitiba - Psicanálise.</t>
+          <t>Sabina Araújo Dos Santos Fagundes, Psicólogo em Curitiba - PR</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1855,7 +1875,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>15 melhores Psicólogos de Curitiba para você e sua família.O Dr. Pedro Elias Sater atende na clínica...</t>
+          <t>Terapia Comportamental. Transtornos em Crianças e Adolescentes. Psicopedagogia Clinica. Altas Habili...</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1865,28 +1885,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.psicanaliseclinica.com/psicologos-de-curitiba/</t>
+          <t>https://agenda.app.br/especialista/sabina-araujo-dos-santos-fagundes-psicologo-curitiba-pr</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(41) 99953-9370</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>554199953937000</t>
-        </is>
-      </c>
+          <t>(CU) 98877-6655</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/20%20melhores%20Psicanalistas%20e%20Psiclogos%20de%20Curi%20curitiba</t>
+          <t>https://www.google.com/maps/search/Sabina%20Arajo%20Dos%20Santos%20Fagundes%2C%20Psiclogo%20curitiba</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da 20 melhores Psicanalistas e Psiclogos de Curi aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Sabina Arajo Dos Santos Fagundes, Psiclogo aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1896,29 +1912,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a 20 melhores Psicanalistas e Psiclogos de Curi?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Sabina Arajo Dos Santos Fagundes, Psiclogo?</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>https://wa.me/554199953937000?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%2020%20melhores%20Psicanalistas%20e%20Psiclogos%20de%20Curi%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Sabina%20Arajo%20Dos%20Santos%20Fagundes%2C%20Psiclogo%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>https://wa.me/554199953937000?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%2020%20melhores%20Psicanalistas%20e%20Psiclogos%20de%20Curi%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Sabina%20Arajo%20Dos%20Santos%20Fagundes%2C%20Psiclogo%3F</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Rumo Clinica de Psicologia e Sade</t>
+          <t>Clnica de Psicologia</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Rumo Clinica de Psicologia e Saúde — psicologo em Curitiba/PR</t>
+          <t>Clínica de Psicologia em Curitiba PR | Clínica EOS</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1933,7 +1949,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Resposta rápida · Sem espera no telefone. A Rumo Clinica de Psicologia e Saúde, em Curitiba/PR, ofer...</t>
+          <t>Entre em contato conosco por telefone, e-mail ou através do nosso site para marcar sua consulta. Est...</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1943,28 +1959,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://velora.tech/pr/curitiba/psicologo/rumo-clinica-de-psicologia-e-saude-287995</t>
+          <t>https://clinicapsieos.com.br/</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>5541325217</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>554132521700</t>
-        </is>
-      </c>
+          <t>(CU) 98877-6655</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Rumo%20Clinica%20de%20Psicologia%20e%20Sade%20curitiba</t>
+          <t>https://www.google.com/maps/search/Clnica%20de%20Psicologia%20curitiba</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Rumo Clinica de Psicologia e Sade aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Clnica de Psicologia aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1974,29 +1986,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Rumo Clinica de Psicologia e Sade?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Clnica de Psicologia?</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>https://wa.me/554132521700?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Rumo%20Clinica%20de%20Psicologia%20e%20Sade%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Clnica%20de%20Psicologia%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>https://wa.me/554132521700?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Rumo%20Clinica%20de%20Psicologia%20e%20Sade%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Clnica%20de%20Psicologia%3F</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Rael Psiclogo</t>
+          <t>Clnica Centro Do Ser / Psicologia / Curitiba</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Rael Psicólogo - Curitiba Centro PR - Telefone... | Bendito Guia</t>
+          <t>Clínica Centro Do Ser / Psicologia / Curitiba</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2011,7 +2023,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Encontre o telefone, endereço e whatsapp de Rael Psicólogo - Curitiba Centro PR em Atibaia. Veja ava...</t>
+          <t>A Clínica Centro do Ser oferece instalações modernas e profissionais de saúde experientes e dedicado...</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2021,24 +2033,28 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.benditoguia.com.br/empresa/rael-psicologo-curitiba-centro-pr</t>
+          <t>https://www.centrodoser.com.br/</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(41) 98516-5591</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5541985165591</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Rael%20Psiclogo%20curitiba</t>
+          <t>https://www.google.com/maps/search/Clnica%20Centro%20Do%20Ser%20/%20Psicologia%20/%20Curitiba%20curitiba</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Rael Psiclogo aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Clnica Centro Do Ser / Psicologia / Curitiba aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2048,29 +2064,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Rael Psiclogo?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Clnica Centro Do Ser / Psicologia / Curitiba?</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Rael%20Psiclogo%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541985165591?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Clnica%20Centro%20Do%20Ser%20/%20Psicologia%20/%20Curitiba%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Rael%20Psiclogo%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541985165591?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Clnica%20Centro%20Do%20Ser%20/%20Psicologia%20/%20Curitiba%3F</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Terapia presencial</t>
+          <t>Tele</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Terapia presencial em Curitiba - Psicologo Rafael Freire</t>
+          <t>Teleconsulta com Psicólogo em Curitiba - PR na Plataforma de...</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2085,7 +2101,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Faça Terapia presencial em Curitiba. Com comodidade, sigilo e segurança, posso ajudar você a ser sua...</t>
+          <t>Agende a sua teleconsulta com Psicólogo na Telemedicina Morsch. Escolha o profissional, dia e horári...</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2095,24 +2111,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://psirafaelfreire.com.br/</t>
+          <t>https://telemedicinamorsch.com.br/especialidade/psicologo/curitiba-pr</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
+          <t>(CU) 98877-6655</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Terapia%20presencial%20curitiba</t>
+          <t>https://www.google.com/maps/search/Tele%20curitiba</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Terapia presencial aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Tele aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2122,29 +2138,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Terapia presencial?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Tele?</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Terapia%20presencial%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Tele%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Terapia%20presencial%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Tele%3F</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Clnica Centro Do Ser / Psicologia / Curitiba</t>
+          <t>Psicologia e Psiquiatria</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Clínica Centro Do Ser / Psicologia / Curitiba</t>
+          <t>Psicologia e Psiquiatria | Curitiba | Clínica Protheus</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2159,7 +2175,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>A Clínica Centro do Ser oferece instalações modernas e profissionais de saúde experientes e dedicado...</t>
+          <t>A Clínica Protheus é um espaço de promoção da Saúde Mental que atende crianças, jovens e adultos nas...</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2169,24 +2185,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.centrodoser.com.br/</t>
+          <t>https://www.clinicaprotheus.com.br/</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
+          <t>(CU) 98877-6655</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Clnica%20Centro%20Do%20Ser%20/%20Psicologia%20/%20Curitiba%20curitiba</t>
+          <t>https://www.google.com/maps/search/Psicologia%20e%20Psiquiatria%20curitiba</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Clnica Centro Do Ser / Psicologia / Curitiba aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Psicologia e Psiquiatria aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2196,29 +2212,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Clnica Centro Do Ser / Psicologia / Curitiba?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Psicologia e Psiquiatria?</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Clnica%20Centro%20Do%20Ser%20/%20Psicologia%20/%20Curitiba%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Psicologia%20e%20Psiquiatria%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Clnica%20Centro%20Do%20Ser%20/%20Psicologia%20/%20Curitiba%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Psicologia%20e%20Psiquiatria%3F</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Clnica de Psicologia</t>
+          <t>Psicologo Curitiba</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Clínica de Psicologia em Curitiba PR | Clínica EOS</t>
+          <t>Psicologo Curitiba - Guilherme Moro | HelpSaúde</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2233,34 +2249,38 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Entre em contato conosco por telefone, e-mail ou através do nosso site para marcar sua consulta. Est...</t>
+          <t>Você já se consultou com Psicologo Curitiba - Guilherme Moro? Conte aqui como foi. Outros pacientes ...</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>SITE ATIVO 📱</t>
+          <t>SITE FORA DO AR / LINK QUEBRADO 🚨</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://clinicapsieos.com.br/</t>
+          <t>https://www.helpsaude.com/guilherme-moro.psicologo.pr0816488</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(41) 9644-0186</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>554196440186</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Clnica%20de%20Psicologia%20curitiba</t>
+          <t>https://www.google.com/maps/search/Psicologo%20Curitiba%20curitiba</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Clnica de Psicologia aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Psicologo Curitiba aí em Curitiba no Google e fui tentar acessar o site de vocês e vi que está fora do ar.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2270,29 +2290,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Clnica de Psicologia?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Psicologo Curitiba?</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Clnica%20de%20Psicologia%20curitiba%20whatsapp</t>
+          <t>https://wa.me/554196440186?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Psicologo%20Curitiba%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20fui%20tentar%20acessar%20o%20site%20de%20voc%C3%AAs%20e%20vi%20que%20est%C3%A1%20fora%20do%20ar.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Clnica%20de%20Psicologia%20curitiba%20whatsapp</t>
+          <t>https://wa.me/554196440186?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Psicologo%20Curitiba%3F</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Psicloga</t>
+          <t>Vagas de Psicologia</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Psicóloga em Curitiba | Elisiane Siqueira - TCC e Terapia Online</t>
+          <t>Vagas de Psicologia em Curitiba, PR | Indeed</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2307,7 +2327,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Psicóloga clínica com 30+ anos. Especialista em TCC e Terapia do Esquema. Atendimento no Cabral e on...</t>
+          <t>Instituição de Saúde e Reabilitação busca profissional Psicólogo em Curitiba (Rebouças). Realizar at...</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2317,28 +2337,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.elisianesiqueira.com.br/</t>
+          <t>https://br.indeed.com/q-psicologia-l-curitiba,-pr-vagas.html</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>5541992396</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>554199239600</t>
-        </is>
-      </c>
+          <t>(CU) 98877-6655</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Psicloga%20curitiba</t>
+          <t>https://www.google.com/maps/search/Vagas%20de%20Psicologia%20curitiba</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Psicloga aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Vagas de Psicologia aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2348,29 +2364,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Psicloga?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Vagas de Psicologia?</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>https://wa.me/554199239600?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Psicloga%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Vagas%20de%20Psicologia%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>https://wa.me/554199239600?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Psicloga%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Vagas%20de%20Psicologia%3F</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Psicologia e Psiquiatria</t>
+          <t>Andre Valente</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Psicologia e Psiquiatria | Curitiba | Clínica Protheus</t>
+          <t>Andre Valente - Psicólogo Clínico na Fundação Estatal de... | Lin</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2385,7 +2401,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>A Clínica Protheus é um espaço de promoção da Saúde Mental que atende crianças, jovens e adultos nas...</t>
+          <t>Psicólogo Residente. Hospital de Clínicas UFPR. fev. de 2013 - mar. de 2015 2 anos 2 meses. Curitiba...</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2395,28 +2411,28 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.clinicaprotheus.com.br/</t>
+          <t>https://br.linkedin.com/in/andre-valente-93281913a</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>41 3019-4363</t>
+          <t>(19) 0745-0980</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>55413019436300</t>
+          <t>551907450980</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Psicologia%20e%20Psiquiatria%20curitiba</t>
+          <t>https://www.google.com/maps/search/Andre%20Valente%20curitiba</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Psicologia e Psiquiatria aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Andre Valente aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2426,29 +2442,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Psicologia e Psiquiatria?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Andre Valente?</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>https://wa.me/55413019436300?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Psicologia%20e%20Psiquiatria%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/551907450980?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Andre%20Valente%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>https://wa.me/55413019436300?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Psicologia%20e%20Psiquiatria%3F</t>
+          <t>https://wa.me/551907450980?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Andre%20Valente%3F</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Clinica de Psicologia</t>
+          <t>Terapia online com psiclogos disponveis 24h p</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Clinica de Psicologia | Dom Clinica Terapeutica | Curitiba</t>
+          <t>Terapia online com psicólogos disponíveis 24h por dia | Zenklub</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2463,7 +2479,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dedicação para realizar, Orientação para transformar, Movimento para se encontrar. ©2023 por DOM Clí...</t>
+          <t>Estamos sempre com você. Todo dia e a qualquer hora, nossos especialistas estarão disponíveis para a...</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2473,24 +2489,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.clinicadom.com/</t>
+          <t>https://zenklub.com.br/</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
+          <t>(CU) 98877-6655</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Clinica%20de%20Psicologia%20curitiba</t>
+          <t>https://www.google.com/maps/search/Terapia%20online%20com%20psiclogos%20disponveis%2024h%20p%20curitiba</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Clinica de Psicologia aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Terapia online com psiclogos disponveis 24h p aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2500,29 +2516,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Clinica de Psicologia?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Terapia online com psiclogos disponveis 24h p?</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Clinica%20de%20Psicologia%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Terapia%20online%20com%20psiclogos%20disponveis%2024h%20p%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Clinica%20de%20Psicologia%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Terapia%20online%20com%20psiclogos%20disponveis%2024h%20p%3F</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Psicanlise e Terapia de Casal Online</t>
+          <t>Web site created using create-react-app</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Psicanálise e Terapia de Casal Online - Jacklen Dantas - Contatos</t>
+          <t>Web site created using create-react-app</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2537,34 +2553,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Consultórios em São Paulo e Curitiba: Curitiba - Praça São Paulo da Cruz, 50 - Juvevê - Curitiba - P...</t>
+          <t>Web site created using create-react-app......</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>SITE ATIVO 📱</t>
+          <t>SITE FORA DO AR / LINK QUEBRADO 🚨</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.jacklendantas.com.br/contatos</t>
+          <t>https://cadunico.dataprev.gov.br/</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
+          <t>(CU) 98877-6655</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Psicanlise%20e%20Terapia%20de%20Casal%20Online%20curitiba</t>
+          <t>https://www.google.com/maps/search/Web%20site%20created%20using%20create-react-app%20curitiba</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Psicanlise e Terapia de Casal Online aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Web site created using create-react-app aí em Curitiba no Google e fui tentar acessar o site de vocês e vi que está fora do ar.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2574,29 +2590,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Psicanlise e Terapia de Casal Online?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Web site created using create-react-app?</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Psicanlise%20e%20Terapia%20de%20Casal%20Online%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Web%20site%20created%20using%20create-react-app%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20fui%20tentar%20acessar%20o%20site%20de%20voc%C3%AAs%20e%20vi%20que%20est%C3%A1%20fora%20do%20ar.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Psicanlise%20e%20Terapia%20de%20Casal%20Online%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Web%20site%20created%20using%20create-react-app%3F</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Network Psicologia</t>
+          <t>Portal</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Network Psicologia</t>
+          <t>Portal - Detran-SP</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2611,7 +2627,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>A Network Psicologia é uma empresa voltada para serviços psicológicos, Avaliações Psicológicas, Orie...</t>
+          <t>O novo Portal do Detran-SP feito pra você! Mais fácil, rápido e digital. Pra você não perder tempo c...</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2621,28 +2637,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://networkpsicologia.com.br/</t>
+          <t>https://www.detran.sp.gov.br/</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(41) 99979-0161</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>554199979016100</t>
-        </is>
-      </c>
+          <t>(CU) 98877-6655</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Network%20Psicologia%20curitiba</t>
+          <t>https://www.google.com/maps/search/Portal%20curitiba</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Network Psicologia aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Portal aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2652,29 +2664,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Network Psicologia?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Portal?</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>https://wa.me/554199979016100?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Network%20Psicologia%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Portal%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>https://wa.me/554199979016100?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Network%20Psicologia%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Portal%3F</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Atendimento Psicolgico Com Preo Acessvel</t>
+          <t>Barbearia</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Atendimento Psicológico Com Preço Acessível - Curitiba - Luana...</t>
+          <t>Barbearia em Curitiba - perto de mim - Cabeleireiro masculino ...</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2689,34 +2701,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Em muitos casos, o psicólogo online torna possível um cuidado que, de outra forma, seria adiado por ...</t>
+          <t>Um recurso incrível que você pode utilizar é o nosso mapa virtual, em que você pode encontrar todas ...</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>SITE FORA DO AR (ERRO 404) 🚨</t>
+          <t>SITE ATIVO 📱</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://psicologaluanaamaral.com.br/psicologo/atendimento-psicologico-com-preco-acessivel-curitiba/</t>
+          <t>https://booksy.com/pt-br/s/barbearias/583853_curitiba</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(41) 3501-0365</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>554135010365</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Atendimento%20Psicolgico%20Com%20Preo%20Acessvel%20curitiba</t>
+          <t>https://www.google.com/maps/search/Barbearia%20curitiba</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Atendimento Psicolgico Com Preo Acessvel aí em Curitiba no Google e fui tentar acessar o site de vocês e vi que está fora do ar.
+Vi o perfil da Barbearia aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2726,29 +2742,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Atendimento Psicolgico Com Preo Acessvel?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Barbearia?</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Atendimento%20Psicolgico%20Com%20Preo%20Acessvel%20curitiba%20whatsapp</t>
+          <t>https://wa.me/554135010365?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Barbearia%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Atendimento%20Psicolgico%20Com%20Preo%20Acessvel%20curitiba%20whatsapp</t>
+          <t>https://wa.me/554135010365?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Barbearia%3F</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Entre em contato agora mesmo com um psiclogo</t>
+          <t>Os melhores barbeiros perto de mim</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Entre em contato agora mesmo com um psicólogo na PsyMeet...</t>
+          <t xml:space="preserve">Os melhores barbeiros perto de mim em Curitiba - FreshaBarbearia </t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2763,7 +2779,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Encontre um psicólogo de acordo com a demanda que você tem e entre em contato imediatamente para age...</t>
+          <t>Agendar online com os melhores Barbeiros perto de você em Curitiba. Excelentes ofertas e descontos! ...</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2773,24 +2789,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.psymeetsocial.com/</t>
+          <t>https://www.fresha.com/lp/pt/bt/barbearias/br-curitiba</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
+          <t>(CU) 98877-6655</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Entre%20em%20contato%20agora%20mesmo%20com%20um%20psiclogo%20curitiba</t>
+          <t>https://www.google.com/maps/search/Os%20melhores%20barbeiros%20perto%20de%20mim%20curitiba</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Entre em contato agora mesmo com um psiclogo aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Os melhores barbeiros perto de mim aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2800,29 +2816,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Entre em contato agora mesmo com um psiclogo?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Os melhores barbeiros perto de mim?</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Entre%20em%20contato%20agora%20mesmo%20com%20um%20psiclogo%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Os%20melhores%20barbeiros%20perto%20de%20mim%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Entre%20em%20contato%20agora%20mesmo%20com%20um%20psiclogo%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Os%20melhores%20barbeiros%20perto%20de%20mim%3F</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Atendimento psiclogo online</t>
+          <t>Barbearia Saint Germain</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Atendimento psicólogo online - Psicovida</t>
+          <t>Barbearia Saint Germain | Curitiba</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2837,7 +2853,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Atendimento psicólogo online é tão eficaz quanto o atendimento presencial, apresentando resultados p...</t>
+          <t>Para quem busca uma barbearia em Curitiba que combine sofisticação, qualidade e atendimento atencios...</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2847,24 +2863,28 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.psicovida.net.br/atendimento-psicologo-online</t>
+          <t>https://www.barbeariasg.com/</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(41) 99894-4124</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>5541998944124</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Atendimento%20psiclogo%20online%20curitiba</t>
+          <t>https://www.google.com/maps/search/Barbearia%20Saint%20Germain%20curitiba</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Atendimento psiclogo online aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Barbearia Saint Germain aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2874,29 +2894,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Atendimento psiclogo online?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Barbearia Saint Germain?</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Atendimento%20psiclogo%20online%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541998944124?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Barbearia%20Saint%20Germain%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Atendimento%20psiclogo%20online%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541998944124?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Barbearia%20Saint%20Germain%3F</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>TANIGUTI PSICLOGO</t>
+          <t>15 Melhores Barbearias no Rebouas</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>TANIGUTI PSICÓLOGO - Atendimento psicológico online</t>
+          <t>15 Melhores Barbearias no Rebouças em Curitiba — Guia 2026</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2911,7 +2931,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Você não precisa lidar com tudo sozinho. Redescubra seu equilíbrio emocional e retome o controle da ...</t>
+          <t>Neste guia reunimos as 15 melhores barbearias no Rebouças, selecionadas com base nas avaliações reai...</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2921,24 +2941,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.tanigutipsicologo.com/</t>
+          <t>https://blog.beard.com.br/barbearias-no-reboucas-curitiba/</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
+          <t>(CU) 98877-6655</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/TANIGUTI%20PSICLOGO%20curitiba</t>
+          <t>https://www.google.com/maps/search/15%20Melhores%20Barbearias%20no%20Rebouas%20curitiba</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da TANIGUTI PSICLOGO aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da 15 Melhores Barbearias no Rebouas aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2948,29 +2968,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a TANIGUTI PSICLOGO?</t>
+Posso te mandar a prévia demonstrativa que fiz para a 15 Melhores Barbearias no Rebouas?</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=TANIGUTI%20PSICLOGO%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%2015%20Melhores%20Barbearias%20no%20Rebouas%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=TANIGUTI%20PSICLOGO%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%2015%20Melhores%20Barbearias%20no%20Rebouas%3F</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Atendimento</t>
+          <t>barbearias</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Atendimento | Psicólogo Online e Presencial em Curitiba</t>
+          <t>barbearias em Curitiba 2026 | OndeAbrir</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2985,34 +3005,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>A tag Atendimento reúne conteúdos relacionados à prática da psicologia clínica, incluindo informaçõe...</t>
+          <t>Panorama competitivo: barbearias em Curitiba. Curitiba tem 1.8M habitantes e um mercado de barbearia...</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>SITE FORA DO AR / LINK QUEBRADO 🚨</t>
+          <t>SITE ATIVO 📱</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://onlinepsi.com.br/tag/atendimento/</t>
+          <t>https://ondeabrir.com/mercado/barbearia/curitiba</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
+          <t>(CU) 98877-6655</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Atendimento%20curitiba</t>
+          <t>https://www.google.com/maps/search/barbearias%20curitiba</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Atendimento aí em Curitiba no Google e fui tentar acessar o site de vocês e vi que está fora do ar.
+Vi o perfil da barbearias aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -3022,29 +3042,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Atendimento?</t>
+Posso te mandar a prévia demonstrativa que fiz para a barbearias?</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Atendimento%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20barbearias%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Atendimento%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20barbearias%3F</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Curso de Noes Bsicas em Atendimento Psiclogo</t>
+          <t>Barbers In Barbearia</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Curso de Noções Básicas em Atendimento Psicólogo Home Care</t>
+          <t>Barbers In Barbearia - Curitiba - Faça Agendamentos Online - Preç</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3059,7 +3079,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>- Introdução ao Atendimento Psicológico em Home Care. - Atendimento Psicológico Domiciliar no Contex...</t>
+          <t>Confira Barbers In Barbearia em Curitiba - explore preços, avaliações e faça agendamentos online 24 ...</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3069,24 +3089,28 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.wreducacional.com.br/curso-de-atendimento-psic-logo-home-care</t>
+          <t>https://booksy.com/pt-br/99716_barbers-in-barbearia_barbearias_583853_curitiba</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(41) 3598-9540</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>554135989540</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Curso%20de%20Noes%20Bsicas%20em%20Atendimento%20Psiclogo%20curitiba</t>
+          <t>https://www.google.com/maps/search/Barbers%20In%20Barbearia%20curitiba</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Curso de Noes Bsicas em Atendimento Psiclogo aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Barbers In Barbearia aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -3096,29 +3120,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Curso de Noes Bsicas em Atendimento Psiclogo?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Barbers In Barbearia?</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Curso%20de%20Noes%20Bsicas%20em%20Atendimento%20Psiclogo%20curitiba%20whatsapp</t>
+          <t>https://wa.me/554135989540?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Barbers%20In%20Barbearia%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Curso%20de%20Noes%20Bsicas%20em%20Atendimento%20Psiclogo%20curitiba%20whatsapp</t>
+          <t>https://wa.me/554135989540?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Barbers%20In%20Barbearia%3F</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Curso de Atendimento Psiclogo Home Care Onlin</t>
+          <t>Melhores Servios de Barbearias</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Curso de Atendimento Psicólogo Home Care Online com Certificado</t>
+          <t>Melhores Serviços de Barbearias em Curitiba, PR | GuiaFix</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3133,7 +3157,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Objetivos do Curso: Agrupar as principais informações para que os interessados sobre a temática poss...</t>
+          <t>Descubra a Soul Barbearia, localizada no Shopping Estação de Curitiba. Nossa barbearia oferece um am...</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3143,24 +3167,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.certificando.com.br/cursos/atendimento-psicologo-home-care.html</t>
+          <t>https://guiafix.com.br/curitiba-pr/barbearias</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
+          <t>(CU) 98877-6655</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Curso%20de%20Atendimento%20Psiclogo%20Home%20Care%20Onlin%20curitiba</t>
+          <t>https://www.google.com/maps/search/Melhores%20Servios%20de%20Barbearias%20curitiba</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Curso de Atendimento Psiclogo Home Care Onlin aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Melhores Servios de Barbearias aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -3170,29 +3194,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Curso de Atendimento Psiclogo Home Care Onlin?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Melhores Servios de Barbearias?</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Curso%20de%20Atendimento%20Psiclogo%20Home%20Care%20Onlin%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Melhores%20Servios%20de%20Barbearias%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Curso%20de%20Atendimento%20Psiclogo%20Home%20Care%20Onlin%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Melhores%20Servios%20de%20Barbearias%3F</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Terapia online com psiclogos disponveis 24h p</t>
+          <t>Barbearia Clube</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Terapia online com psicólogos disponíveis 24h por dia | Zenklub</t>
+          <t>Barbearia Clube | Tradição e Excelência em Curitiba (Mercês)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3207,7 +3231,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Estamos sempre com você. Todo dia e a qualquer hora, nossos especialistas estarão disponíveis para a...</t>
+          <t>A barbearia clássica preferida de Curitiba. Barbearia Clube: Barba na navalha, cortes visagistas, Di...</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3217,24 +3241,28 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://zenklub.com.br/</t>
+          <t>https://barbeariaclube.com.br/</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(41) 3014-9413</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>554130149413</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Terapia%20online%20com%20psiclogos%20disponveis%2024h%20p%20curitiba</t>
+          <t>https://www.google.com/maps/search/Barbearia%20Clube%20curitiba</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Terapia online com psiclogos disponveis 24h p aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Barbearia Clube aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -3244,29 +3272,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Terapia online com psiclogos disponveis 24h p?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Barbearia Clube?</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Terapia%20online%20com%20psiclogos%20disponveis%2024h%20p%20curitiba%20whatsapp</t>
+          <t>https://wa.me/554130149413?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Barbearia%20Clube%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Terapia%20online%20com%20psiclogos%20disponveis%2024h%20p%20curitiba%20whatsapp</t>
+          <t>https://wa.me/554130149413?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Barbearia%20Clube%3F</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Portal</t>
+          <t>AutoRank para Barbearias</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Portal - Detran-SP</t>
+          <t>AutoRank para Barbearias em Curitiba | Seu Negócio na Primeira...</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3281,7 +3309,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>O novo Portal do Detran-SP feito pra você! Mais fácil, rápido e digital. Pra você não perder tempo c...</t>
+          <t>Barbearias em Curitiba. Coloque sua barbearia na primeira página do Google e atraia clientes buscand...</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -3291,28 +3319,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.detran.sp.gov.br/</t>
+          <t>https://www.autorank.com.br/barbearia/curitiba</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(41) 3350-8484</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>55413350848400</t>
-        </is>
-      </c>
+          <t>(CU) 98877-6655</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Portal%20curitiba</t>
+          <t>https://www.google.com/maps/search/AutoRank%20para%20Barbearias%20curitiba</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Portal aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da AutoRank para Barbearias aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -3322,29 +3346,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Portal?</t>
+Posso te mandar a prévia demonstrativa que fiz para a AutoRank para Barbearias?</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>https://wa.me/55413350848400?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Portal%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20AutoRank%20para%20Barbearias%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>https://wa.me/55413350848400?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Portal%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20AutoRank%20para%20Barbearias%3F</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>"Barber shop" in Curitiba</t>
+          <t>Shelby Barbearia</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>"Barber shop" in Curitiba - Search in Google Maps</t>
+          <t>Shelby Barbearia - (41) 98475-3472 BARBEARIA EM CURITIBA...</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3359,38 +3383,38 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>You're seeing a limited view of Google Maps. Barbearia Visconde, Barbearia John Six - Bigorrilho, Ba...</t>
+          <t>Há 6 anos, a Shelby Barbearia vem construindo uma história de dedicação, estilo e excelência em Curi...</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>SEM SITE (OPORTUNIDADE QUENTE 🔥)</t>
+          <t>SITE ATIVO 📱</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sem Site Cadastrado</t>
+          <t>https://barbeariashelby.com.br/sobre-nos/</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(95) 81084575</t>
+          <t>(41) 98475-3472</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>55958108457500</t>
+          <t>5541984753472</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/%22Barber%20shop%22%20in%20Curitiba%20curitiba</t>
+          <t>https://www.google.com/maps/search/Shelby%20Barbearia%20curitiba</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da "Barber shop" in Curitiba aí em Curitiba no Google e vi que vocês ainda não têm um site próprio para celular.
+Vi o perfil da Shelby Barbearia aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -3400,29 +3424,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a "Barber shop" in Curitiba?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Shelby Barbearia?</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>https://wa.me/55958108457500?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20%22Barber%20shop%22%20in%20Curitiba%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20voc%C3%AAs%20ainda%20n%C3%A3o%20t%C3%AAm%20um%20site%20pr%C3%B3prio%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541984753472?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Shelby%20Barbearia%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>https://wa.me/55958108457500?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20%22Barber%20shop%22%20in%20Curitiba%3F</t>
+          <t>https://wa.me/5541984753472?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Shelby%20Barbearia%3F</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Barbearia</t>
+          <t>Barbearia John Six</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Barbearia em Curitiba - perto de mim - Cabeleireiro masculino ...</t>
+          <t>Barbearia John Six - Bigorrilho em Curitiba - PR | Locais do Bras</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3437,7 +3461,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Um recurso incrível que você pode utilizar é o nosso mapa virtual, em que você pode encontrar todas ...</t>
+          <t>Barbearia John Six - Bigorrilho atua no ramo de Barbearia, horário de funcionamento quarta a quinta-...</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3447,24 +3471,28 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://booksy.com/pt-br/s/barbearias/583853_curitiba</t>
+          <t>https://www.locaisdobrasil.com.br/encontre/barbearia/curitiba-pr/barbearia-john-six-bigorrilho/61cf4338c76c53fe0914d004</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(41) 99553-7410</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>5541995537410</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Barbearia%20curitiba</t>
+          <t>https://www.google.com/maps/search/Barbearia%20John%20Six%20curitiba</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Barbearia aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Barbearia John Six aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -3474,29 +3502,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Barbearia?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Barbearia John Six?</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Barbearia%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541995537410?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Barbearia%20John%20Six%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Barbearia%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541995537410?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Barbearia%20John%20Six%3F</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Barbearia Saint Germain</t>
+          <t>CNPJ 53.441.822/0001-74</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Barbearia Saint Germain | Curitiba</t>
+          <t>CNPJ 53.441.822/0001-74 - barbearia curitiba ltda | CNPJ go!</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3511,7 +3539,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Para quem busca uma barbearia em Curitiba que combine sofisticação, qualidade e atendimento atencios...</t>
+          <t>Enriqueça empresas com Google Maps, Instagram, LinkedIn e mais. A IA gera pitchs personalizados para...</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3521,24 +3549,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.barbeariasg.com/</t>
+          <t>https://cnpjgo.com.br/cnpj/53441822000174</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
+          <t>(CU) 98877-6655</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Barbearia%20Saint%20Germain%20curitiba</t>
+          <t>https://www.google.com/maps/search/CNPJ%2053.441.822/0001-74%20curitiba</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Barbearia Saint Germain aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da CNPJ 53.441.822/0001-74 aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -3548,29 +3576,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Barbearia Saint Germain?</t>
+Posso te mandar a prévia demonstrativa que fiz para a CNPJ 53.441.822/0001-74?</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Barbearia%20Saint%20Germain%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20CNPJ%2053.441.822/0001-74%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Barbearia%20Saint%20Germain%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20CNPJ%2053.441.822/0001-74%3F</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Barbearia perto de mim</t>
+          <t>Victor Hugo Barbeiro da Lenno Barbearia</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Barbearia perto de mim em Curitiba - PR</t>
+          <t>Victor Hugo Barbeiro da Lenno Barbearia - Curitiba 2017 - YouTube</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3585,34 +3613,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aqui você encontra uma seleção completa das melhores Barbearia próximas da sua localização, com aval...</t>
+          <t>© 2025 Google LLC....</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>SITE ATIVO 📱</t>
+          <t>SEM SITE PRÓPRIO (OPORTUNIDADE 🔥)</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.locaisdobrasil.com.br/encontre/barbearia-perto-de-mim-em-curitiba-pr</t>
+          <t>Sem Site Cadastrado</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
+          <t>(CU) 98877-6655</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Barbearia%20perto%20de%20mim%20curitiba</t>
+          <t>https://www.google.com/maps/search/Victor%20Hugo%20Barbeiro%20da%20Lenno%20Barbearia%20curitiba</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Barbearia perto de mim aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Victor Hugo Barbeiro da Lenno Barbearia aí em Curitiba no Google e vi que vocês ainda não têm um site próprio para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -3622,29 +3650,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Barbearia perto de mim?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Victor Hugo Barbeiro da Lenno Barbearia?</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Barbearia%20perto%20de%20mim%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Victor%20Hugo%20Barbeiro%20da%20Lenno%20Barbearia%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20voc%C3%AAs%20ainda%20n%C3%A3o%20t%C3%AAm%20um%20site%20pr%C3%B3prio%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Barbearia%20perto%20de%20mim%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Victor%20Hugo%20Barbeiro%20da%20Lenno%20Barbearia%3F</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Os melhores barbeiros perto de mim</t>
+          <t>Link to instagram.com</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Os melhores barbeiros perto de mim em Curitiba - Fresha</t>
+          <t>Link to instagram.com</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3659,34 +3687,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Agendar online com os melhores Barbeiros perto de você em Curitiba. Excelentes ofertas e descontos! ...</t>
+          <t>The site owner hides the web page description....</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>SITE ATIVO 📱</t>
+          <t>SEM SITE PRÓPRIO (OPORTUNIDADE 🔥)</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.fresha.com/lp/pt/bt/barbearias/br-curitiba</t>
+          <t>Sem Site Cadastrado</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
+          <t>(CU) 98877-6655</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Os%20melhores%20barbeiros%20perto%20de%20mim%20curitiba</t>
+          <t>https://www.google.com/maps/search/Link%20to%20instagram.com%20curitiba</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Os melhores barbeiros perto de mim aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Link to instagram.com aí em Curitiba no Google e vi que vocês ainda não têm um site próprio para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -3696,699 +3724,17 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Os melhores barbeiros perto de mim?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Link to instagram.com?</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Os%20melhores%20barbeiros%20perto%20de%20mim%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Link%20to%20instagram.com%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20voc%C3%AAs%20ainda%20n%C3%A3o%20t%C3%AAm%20um%20site%20pr%C3%B3prio%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Os%20melhores%20barbeiros%20perto%20de%20mim%20curitiba%20whatsapp</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Mercado de Barbearia em Centro, Curitiba 2026</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Mercado de Barbearia em Centro, Curitiba 2026 | OndeAbrir</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Curitiba</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Centro / Região</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Mercado de barbearias em Centro, Curitiba: como está em 2026? Cenário competitivo de barbearias em C...</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>SITE ATIVO 📱</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>https://ondeabrir.com/mercado/barbearia/curitiba/centro</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>WhatsApp no Maps 📍</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/Mercado%20de%20Barbearia%20em%20Centro%2C%20Curitiba%202026%20curitiba</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Mercado de Barbearia em Centro, Curitiba 2026 aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
-Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
-Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
-A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
-Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Mercado de Barbearia em Centro, Curitiba 2026?</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=Mercado%20de%20Barbearia%20em%20Centro%2C%20Curitiba%202026%20curitiba%20whatsapp</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=Mercado%20de%20Barbearia%20em%20Centro%2C%20Curitiba%202026%20curitiba%20whatsapp</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Shelby Barbearia</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Shelby Barbearia - (41) 98475-3472 BARBEARIA EM CURITIBA...</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Curitiba</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Centro / Região</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Há 6 anos, a Shelby Barbearia vem construindo uma história de dedicação, estilo e excelência em Curi...</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>SITE ATIVO 📱</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>https://barbeariashelby.com.br/</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>(41) 98475-3472</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>554198475347200</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/Shelby%20Barbearia%20curitiba</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Shelby Barbearia aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
-Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
-Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
-A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
-Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Shelby Barbearia?</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>https://wa.me/554198475347200?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Shelby%20Barbearia%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>https://wa.me/554198475347200?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Shelby%20Barbearia%3F</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Barbers In Barbearia</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Barbers In Barbearia - Curitiba - Faça Agendamentos Online - Preç</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Curitiba</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Centro / Região</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Confira Barbers In Barbearia em Curitiba - explore preços, avaliações e faça agendamentos online 24 ...</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>SITE ATIVO 📱</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>https://booksy.com/pt-br/99716_barbers-in-barbearia_barbearias_583853_curitiba</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>41 3598-9540</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>55413598954000</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/Barbers%20In%20Barbearia%20curitiba</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Barbers In Barbearia aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
-Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
-Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
-A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
-Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Barbers In Barbearia?</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>https://wa.me/55413598954000?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Barbers%20In%20Barbearia%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>https://wa.me/55413598954000?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Barbers%20In%20Barbearia%3F</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Home - Barbearia Vintage</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Curitiba</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Centro / Região</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Depoimentos da barbearia. Melhor barbearia em Curitiba que eu já fui! A barbearia possui estacioname...</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>SITE ATIVO 📱</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>https://barbeariavintage.com.br/</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>WhatsApp no Maps 📍</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/Home%20curitiba</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Home aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
-Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
-Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
-A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
-Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Home?</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=Home%20curitiba%20whatsapp</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=Home%20curitiba%20whatsapp</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Barbearia Clube</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Barbearia Clube | Tradição e Excelência em Curitiba (Mercês)</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Curitiba</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Centro / Região</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>A barbearia clássica preferida de Curitiba. Barbearia Clube: Barba na navalha, cortes visagistas, Di...</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>SITE ATIVO 📱</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>https://barbeariaclube.com.br/</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>(41) 3014-9413</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>55413014941300</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/Barbearia%20Clube%20curitiba</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Barbearia Clube aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
-Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
-Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
-A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
-Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Barbearia Clube?</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>https://wa.me/55413014941300?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Barbearia%20Clube%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>https://wa.me/55413014941300?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Barbearia%20Clube%3F</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Barbearias</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Barbearias em Curitiba, PR — Agende Online | AgendZap | AgendZap</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Curitiba</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Centro / Região</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Quando alguem buscar "barbearia em Curitiba" no Google, SEU negocio vai ser o primeiro resultado. Ag...</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>SITE ATIVO 📱</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>https://agendzap.com.br/encontrar/curitiba/barbearia</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>(41) 99894-4124</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>554199894412400</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/Barbearias%20curitiba</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Barbearias aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
-Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
-Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
-A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
-Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Barbearias?</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>https://wa.me/554199894412400?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Barbearias%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>https://wa.me/554199894412400?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Barbearias%3F</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Melhores Servios de Barbearias</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Melhores Serviços de Barbearias em Curitiba, PR | GuiaFix</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Curitiba</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Centro / Região</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Descubra a Soul Barbearia, localizada no Shopping Estação de Curitiba. Nossa barbearia oferece um am...</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>SITE ATIVO 📱</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>https://guiafix.com.br/curitiba-pr/barbearias</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>WhatsApp no Maps 📍</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/Melhores%20Servios%20de%20Barbearias%20curitiba</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Melhores Servios de Barbearias aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
-Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
-Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
-A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
-Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Melhores Servios de Barbearias?</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=Melhores%20Servios%20de%20Barbearias%20curitiba%20whatsapp</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=Melhores%20Servios%20de%20Barbearias%20curitiba%20whatsapp</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>AutoRank para Barbearias</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>AutoRank para Barbearias em Curitiba | Seu Negócio na Primeira...</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Curitiba</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Centro / Região</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Barbearias em Curitiba. Coloque sua barbearia na primeira página do Google e atraia clientes buscand...</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>SITE ATIVO 📱</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>https://www.autorank.com.br/barbearia/curitiba</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>WhatsApp no Maps 📍</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/AutoRank%20para%20Barbearias%20curitiba</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da AutoRank para Barbearias aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
-Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
-Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
-A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
-Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a AutoRank para Barbearias?</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=AutoRank%20para%20Barbearias%20curitiba%20whatsapp</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=AutoRank%20para%20Barbearias%20curitiba%20whatsapp</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Victor Hugo Barbeiro da Lenno Barbearia</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Victor Hugo Barbeiro da Lenno Barbearia - Curitiba 2017 - YouTube</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Curitiba</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Centro / Região</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>© 2025 Google LLC....</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>SEM SITE (OPORTUNIDADE QUENTE 🔥)</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Sem Site Cadastrado</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>WhatsApp no Maps 📍</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/Victor%20Hugo%20Barbeiro%20da%20Lenno%20Barbearia%20curitiba</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Victor Hugo Barbeiro da Lenno Barbearia aí em Curitiba no Google e vi que vocês ainda não têm um site próprio para celular.
-Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
-Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
-A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
-Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Victor Hugo Barbeiro da Lenno Barbearia?</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=Victor%20Hugo%20Barbeiro%20da%20Lenno%20Barbearia%20curitiba%20whatsapp</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=Victor%20Hugo%20Barbeiro%20da%20Lenno%20Barbearia%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Link%20to%20instagram.com%3F</t>
         </is>
       </c>
     </row>

--- a/leads_psicologo_curitiba.xlsx
+++ b/leads_psicologo_curitiba.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N44"/>
+  <dimension ref="A1:N38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,12 +491,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20 psiclogos</t>
+          <t>Psicloga online / Psicloga Curitiba</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20 psicólogos em Curitiba para apoio emocional</t>
+          <t>Psicóloga online / Psicóloga Curitiba - Psicóloga Amanda Amarante</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -511,7 +511,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Se você está buscando psicólogos em Curitiba, aqui você encontra profissionais preparados para te at...</t>
+          <t>A Psicoterapeuta Amanda Amarante. psicologa curitiba. Olá, sou a Amanda. Psicóloga, formada pela PUC...</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -521,7 +521,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://mindee.com.br/psicologos/curitiba-pr</t>
+          <t>https://www.psicologaamandaamarante.com.br/</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -532,13 +532,13 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/20%20psiclogos%20curitiba</t>
+          <t>https://www.google.com/maps/search/Psicloga%20online%20/%20Psicloga%20Curitiba%20curitiba</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da 20 psiclogos aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Psicloga online / Psicloga Curitiba aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -548,29 +548,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a 20 psiclogos?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Psicloga online / Psicloga Curitiba?</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%2020%20psiclogos%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Psicloga%20online%20/%20Psicloga%20Curitiba%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%2020%20psiclogos%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Psicloga%20online%20/%20Psicloga%20Curitiba%3F</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Psicloga online / Psicloga Curitiba</t>
+          <t>AutoRank para Psiclogos</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Psicóloga online / Psicóloga Curitiba - Psicóloga Amanda Amarante</t>
+          <t>AutoRank para Psicólogos em Curitiba | Seu Consultório na Primeir</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>A Psicoterapeuta Amanda Amarante. psicologa curitiba. Olá, sou a Amanda. Psicóloga, formada pela PUC...</t>
+          <t>Psicólogos em Curitiba. Pacientes buscando psicólogo, terapia, ansiedade e depressão te encontram no...</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.psicologaamandaamarante.com.br/</t>
+          <t>https://www.autorank.com.br/psicologo/curitiba</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -606,13 +606,13 @@
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Psicloga%20online%20/%20Psicloga%20Curitiba%20curitiba</t>
+          <t>https://www.google.com/maps/search/AutoRank%20para%20Psiclogos%20curitiba</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Psicloga online / Psicloga Curitiba aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da AutoRank para Psiclogos aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -622,29 +622,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Psicloga online / Psicloga Curitiba?</t>
+Posso te mandar a prévia demonstrativa que fiz para a AutoRank para Psiclogos?</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Psicloga%20online%20/%20Psicloga%20Curitiba%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20AutoRank%20para%20Psiclogos%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Psicloga%20online%20/%20Psicloga%20Curitiba%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20AutoRank%20para%20Psiclogos%3F</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>psicologo</t>
+          <t>10 melhores psiclogos para Curitiba</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>psicologo em Curitiba/PR — 1787 profissionais — Velora</t>
+          <t>10 melhores psicólogos para Curitiba</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>psicologo em Curitiba. 1787 profissionais encontrados em Curitiba/PR. Não sabe qual escolher? A Piet...</t>
+          <t>Nossos melhores psicólogos em Curitiba, avaliados pela comunidade StarOfService - Curitiba, Paraná.P...</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -669,28 +669,28 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://velora.tech/pr/curitiba/psicologo/</t>
+          <t>https://www.starofservice.com.br/dir/parana/curitiba/curitiba/psicologia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(41) 99644-0186</t>
+          <t>(41) 99953-9370</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5541996440186</t>
+          <t>5541999539370</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/psicologo%20curitiba</t>
+          <t>https://www.google.com/maps/search/10%20melhores%20psiclogos%20para%20Curitiba%20curitiba</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da psicologo aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da 10 melhores psiclogos para Curitiba aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -700,29 +700,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a psicologo?</t>
+Posso te mandar a prévia demonstrativa que fiz para a 10 melhores psiclogos para Curitiba?</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://wa.me/5541996440186?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20psicologo%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541999539370?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%2010%20melhores%20psiclogos%20para%20Curitiba%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>https://wa.me/5541996440186?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20psicologo%3F</t>
+          <t>https://wa.me/5541999539370?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%2010%20melhores%20psiclogos%20para%20Curitiba%3F</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AutoRank para Psiclogos</t>
+          <t>Em busca de um psiclogo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AutoRank para Psicólogos em Curitiba | Seu Consultório na Primeir</t>
+          <t>Em busca de um psicólogo em Curitiba? Consulte os convênios...</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Psicólogos em Curitiba. Pacientes buscando psicólogo, terapia, ansiedade e depressão te encontram no...</t>
+          <t>Conectamos você ao psicólogo ideal para seu objetivo. Consulta presencial e online. Esclareça suas d...</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.autorank.com.br/psicologo/curitiba</t>
+          <t>https://psicologo.curitiba.br/</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -758,13 +758,13 @@
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/AutoRank%20para%20Psiclogos%20curitiba</t>
+          <t>https://www.google.com/maps/search/Em%20busca%20de%20um%20psiclogo%20curitiba</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da AutoRank para Psiclogos aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Em busca de um psiclogo aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -774,29 +774,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a AutoRank para Psiclogos?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Em busca de um psiclogo?</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20AutoRank%20para%20Psiclogos%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Em%20busca%20de%20um%20psiclogo%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20AutoRank%20para%20Psiclogos%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Em%20busca%20de%20um%20psiclogo%3F</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Psiclogos, Clnicas de Psicologia na Cidade de</t>
+          <t>20 psiclogos</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Psicólogos, Clínicas de Psicologia na Cidade de Curitiba - Paraná</t>
+          <t>20 psicólogos em Curitiba para apoio emocional</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>psicologo curitiba gratuito. clinica de psicologia em curitiba.psicologo curitiba amil. psicólogas e...</t>
+          <t>Se você está buscando psicólogos em Curitiba, aqui você encontra profissionais preparados para te at...</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.encontracuritiba.com.br/p/psicologa-em-curitiba.shtml</t>
+          <t>https://mindee.com.br/psicologos/curitiba-pr</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -832,13 +832,13 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Psiclogos%2C%20Clnicas%20de%20Psicologia%20na%20Cidade%20de%20curitiba</t>
+          <t>https://www.google.com/maps/search/20%20psiclogos%20curitiba</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Psiclogos, Clnicas de Psicologia na Cidade de aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da 20 psiclogos aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -848,17 +848,17 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Psiclogos, Clnicas de Psicologia na Cidade de?</t>
+Posso te mandar a prévia demonstrativa que fiz para a 20 psiclogos?</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Psiclogos%2C%20Clnicas%20de%20Psicologia%20na%20Cidade%20de%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%2020%20psiclogos%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Psiclogos%2C%20Clnicas%20de%20Psicologia%20na%20Cidade%20de%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%2020%20psiclogos%3F</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Psicologias / Psiclogos</t>
+          <t>Stelmach Psicologia</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Psicologias / Psicólogos em Curitiba, PR — WhatsApp</t>
+          <t>Stelmach Psicologia | Gestalt-Terapia e Psicanálise</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -959,34 +959,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Veja os psicólogos mais bem avaliados em Curitiba, PR. Terapia individual, de casal, infantil, avali...</t>
+          <t>Psicólogo clínico com especialização em estresse, doenças psicossomáticas e autoimunes. Grupos de de...</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SEM SITE (OPORTUNIDADE QUENTE 🔥)</t>
+          <t>SITE ATIVO 📱</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sem Site Cadastrado</t>
+          <t>https://www.stelmach.psc.br/</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(CU) 98877-6655</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(41) 9219-2223</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>554192192223</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Psicologias%20/%20Psiclogos%20curitiba</t>
+          <t>https://www.google.com/maps/search/Stelmach%20Psicologia%20curitiba</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Psicologias / Psiclogos aí em Curitiba no Google e vi que vocês ainda não têm um site próprio para celular.
+Vi o perfil da Stelmach Psicologia aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -996,29 +1000,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Psicologias / Psiclogos?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Stelmach Psicologia?</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Psicologias%20/%20Psiclogos%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20voc%C3%AAs%20ainda%20n%C3%A3o%20t%C3%AAm%20um%20site%20pr%C3%B3prio%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/554192192223?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Stelmach%20Psicologia%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Psicologias%20/%20Psiclogos%3F</t>
+          <t>https://wa.me/554192192223?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Stelmach%20Psicologia%3F</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Psicloga</t>
+          <t>Link to facebook.com</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Psicóloga em Curitiba | Psicoterapia Online | Isabela Cazé</t>
+          <t>Link to facebook.com</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1033,38 +1037,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Atendimento presencial em Curitiba e online para adolescentes, adultos, casais e famílias, com enfoq...</t>
+          <t>The site owner hides the web page description....</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SITE ATIVO 📱</t>
+          <t>SEM SITE PRÓPRIO (OPORTUNIDADE 🔥)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://isabelacazepsicologa.com/</t>
+          <t>Sem Site Cadastrado</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(11) 98723-2712</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5511987232712</t>
-        </is>
-      </c>
+          <t>(CU) 98877-6655</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Psicloga%20curitiba</t>
+          <t>https://www.google.com/maps/search/Link%20to%20facebook.com%20curitiba</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Psicloga aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Link to facebook.com aí em Curitiba no Google e vi que vocês ainda não têm um site próprio para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1074,29 +1074,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Psicloga?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Link to facebook.com?</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://wa.me/5511987232712?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Psicloga%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Link%20to%20facebook.com%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20voc%C3%AAs%20ainda%20n%C3%A3o%20t%C3%AAm%20um%20site%20pr%C3%B3prio%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://wa.me/5511987232712?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Psicloga%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Link%20to%20facebook.com%3F</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Psiclogos, Curitiba, PR</t>
+          <t>Psicologo</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Psicólogos, Curitiba, PR - Central Terapia</t>
+          <t>Psicologo | Curitiba | PsicoEliPassos</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1111,38 +1111,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Psicólogos perto de você! Obtenha suporte e consulta especializada com os mais recomendados psicólog...</t>
+          <t>Artigos. Blog | PsicoEliPassos | Curitiba. Contato....</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SITE ATIVO 📱</t>
+          <t>SITE FORA DO AR (ERRO 404) 🚨</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://centralterapia.com.br/psicologo/curitiba-pr/</t>
+          <t>https://www.psicoelipassos.com.br/</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>41999756</t>
+          <t>(41) 98484-0002</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5541999756</t>
+          <t>5541984840002</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Psiclogos%2C%20Curitiba%2C%20PR%20curitiba</t>
+          <t>https://www.google.com/maps/search/Psicologo%20curitiba</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Psiclogos, Curitiba, PR aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Psicologo aí em Curitiba no Google e fui tentar acessar o site de vocês e vi que está fora do ar.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1152,29 +1152,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Psiclogos, Curitiba, PR?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Psicologo?</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://wa.me/5541999756?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Psiclogos%2C%20Curitiba%2C%20PR%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541984840002?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Psicologo%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20fui%20tentar%20acessar%20o%20site%20de%20voc%C3%AAs%20e%20vi%20que%20est%C3%A1%20fora%20do%20ar.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://wa.me/5541999756?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Psiclogos%2C%20Curitiba%2C%20PR%3F</t>
+          <t>https://wa.me/5541984840002?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Psicologo%3F</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Leonardo Fd Araujo</t>
+          <t>Emily Ann Francisco Blum</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Leonardo Fd Araujo | Psicólogo em Curitiba | Bigorrilho</t>
+          <t>Emily Ann Francisco Blum — psicologo em Curitiba/PR</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Psicólogo em Curitiba, com experiência em psicoterapia, avaliação psicológica, elaboração de laudos ...</t>
+          <t>Emily Ann Francisco Blum é psicóloga em Curitiba/PR, oferecendo um atendimento acolhedor e atento às...</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1199,28 +1199,28 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://psicologoemcuritiba.com.br/</t>
+          <t>https://velora.tech/pr/curitiba/psicologo/emily-ann-francisco-blum-288247/</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(41) 99643-9560</t>
+          <t>(41) 3248-4551</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5541996439560</t>
+          <t>554132484551</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Leonardo%20Fd%20Araujo%20curitiba</t>
+          <t>https://www.google.com/maps/search/Emily%20Ann%20Francisco%20Blum%20curitiba</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Leonardo Fd Araujo aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Emily Ann Francisco Blum aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1230,29 +1230,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Leonardo Fd Araujo?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Emily Ann Francisco Blum?</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://wa.me/5541996439560?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Leonardo%20Fd%20Araujo%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/554132484551?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Emily%20Ann%20Francisco%20Blum%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>https://wa.me/5541996439560?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Leonardo%20Fd%20Araujo%3F</t>
+          <t>https://wa.me/554132484551?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Emily%20Ann%20Francisco%20Blum%3F</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>Psiclogo, Curitiba, PR</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ITC - Instituto Terapêutico de Curitiba — psicologo em Curitiba/P</t>
+          <t>Psicólogo, Curitiba, PR - Rede Psicólogos</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Resposta rápida pelo WhatsApp. A ITC - Instituto Terapêutico de Curitiba oferece atendimento com psi...</t>
+          <t>Curitiba. Procurando um Psicólogo(a) perto de você?Envie um WhatsApp diretamente para a(o) psicóloga...</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1277,28 +1277,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://velora.tech/pr/curitiba/psicologo/itc-instituto-terapeutico-de-curitiba-288248</t>
+          <t>https://redepsicologos.com.br/psicologo/curitiba/</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>41301914</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5541301914</t>
-        </is>
-      </c>
+          <t>(CU) 98877-6655</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/ITC%20curitiba</t>
+          <t>https://www.google.com/maps/search/Psiclogo%2C%20Curitiba%2C%20PR%20curitiba</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da ITC aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Psiclogo, Curitiba, PR aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1308,29 +1304,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a ITC?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Psiclogo, Curitiba, PR?</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://wa.me/5541301914?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20ITC%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Psiclogo%2C%20Curitiba%2C%20PR%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>https://wa.me/5541301914?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20ITC%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Psiclogo%2C%20Curitiba%2C%20PR%3F</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>104 avaliaes sobre Psicloga Infantil</t>
+          <t>Salrio: Psicologo</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>104 avaliações sobre Psicóloga Infantil | Especialista em Curitib</t>
+          <t>Salário: Psicologo em Curitiba 2026 | Glassdoor</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1345,7 +1341,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Situada em Curitiba (Paraná). Clique e confira as informações e comentários.A dra. é muito atenciosa...</t>
+          <t>A média salarial de Psicologo é de R$ 8.146 na cidade: Curitiba. Clique aqui para ver a remuneração ...</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1355,28 +1351,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://avaliacoesbrasil.com/psicologo/curitiba/psicologa-infantil-especialist/</t>
+          <t>https://www.glassdoor.com.br/Salários/curitiba-psicologo-salário-SRCH_IL.0,8_IC2387909_KO9,18.htm</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(41) 3585-1481</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>554135851481</t>
-        </is>
-      </c>
+          <t>(CU) 98877-6655</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/104%20avaliaes%20sobre%20Psicloga%20Infantil%20curitiba</t>
+          <t>https://www.google.com/maps/search/Salrio%3A%20Psicologo%20curitiba</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da 104 avaliaes sobre Psicloga Infantil aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Salrio: Psicologo aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1386,29 +1378,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a 104 avaliaes sobre Psicloga Infantil?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Salrio: Psicologo?</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>https://wa.me/554135851481?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20104%20avaliaes%20sobre%20Psicloga%20Infantil%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Salrio%3A%20Psicologo%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://wa.me/554135851481?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20104%20avaliaes%20sobre%20Psicloga%20Infantil%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Salrio%3A%20Psicologo%3F</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Hudson Padilha • Psiclogo Curitiba. Psicanali</t>
+          <t>Psiclogos, Clnicas de Psicologia na Cidade de</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hudson Padilha • Psicólogo Curitiba. Psicanalista ...</t>
+          <t>Psicólogos, Clínicas de Psicologia na Cidade de Curitiba - Paraná</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1423,7 +1415,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hudson é Psicanalista e Psicólogo (CRP:08/36638) com especialização em Psicanálise: Sujeito e Cultur...</t>
+          <t>psicologo curitiba gratuito. clinica de psicologia em curitiba.psicologo curitiba amil. psicólogas e...</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1433,24 +1425,28 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.hudsonpadilha.com/</t>
+          <t>https://www.encontracuritiba.com.br/p/psicologa-em-curitiba.shtml</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(CU) 98877-6655</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(41) 3223-8630</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>554132238630</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Hudson%20Padilha%20%E2%80%A2%20Psiclogo%20Curitiba.%20Psicanali%20curitiba</t>
+          <t>https://www.google.com/maps/search/Psiclogos%2C%20Clnicas%20de%20Psicologia%20na%20Cidade%20de%20curitiba</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Hudson Padilha • Psiclogo Curitiba. Psicanali aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Psiclogos, Clnicas de Psicologia na Cidade de aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1460,29 +1456,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Hudson Padilha • Psiclogo Curitiba. Psicanali?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Psiclogos, Clnicas de Psicologia na Cidade de?</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Hudson%20Padilha%20%E2%80%A2%20Psiclogo%20Curitiba.%20Psicanali%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/554132238630?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Psiclogos%2C%20Clnicas%20de%20Psicologia%20na%20Cidade%20de%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Hudson%20Padilha%20%E2%80%A2%20Psiclogo%20Curitiba.%20Psicanali%3F</t>
+          <t>https://wa.me/554132238630?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Psiclogos%2C%20Clnicas%20de%20Psicologia%20na%20Cidade%20de%3F</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Link to facebook.com</t>
+          <t>Network Psicologia</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Link to facebook.com</t>
+          <t>Network Psicologia</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1497,34 +1493,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>The site owner hides the web page description....</t>
+          <t>Fundada Pela Psicóloga Jucele Antunes (CRP 15.284/PR), desde 2012, está situada em Curitiba, com ate...</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SEM SITE PRÓPRIO (OPORTUNIDADE 🔥)</t>
+          <t>SITE ATIVO 📱</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sem Site Cadastrado</t>
+          <t>https://networkpsicologia.com.br/</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(CU) 98877-6655</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(41) 99866-3402</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5541998663402</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Link%20to%20facebook.com%20curitiba</t>
+          <t>https://www.google.com/maps/search/Network%20Psicologia%20curitiba</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Link to facebook.com aí em Curitiba no Google e vi que vocês ainda não têm um site próprio para celular.
+Vi o perfil da Network Psicologia aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1534,29 +1534,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Link to facebook.com?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Network Psicologia?</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Link%20to%20facebook.com%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20voc%C3%AAs%20ainda%20n%C3%A3o%20t%C3%AAm%20um%20site%20pr%C3%B3prio%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541998663402?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Network%20Psicologia%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Link%20to%20facebook.com%3F</t>
+          <t>https://wa.me/5541998663402?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Network%20Psicologia%3F</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20 melhores Psicanalistas e Psiclogos de Curi</t>
+          <t>Blog de Psicologia</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>20 melhores Psicanalistas e Psicólogos de Curitiba - Psicanálise.</t>
+          <t>Blog de Psicologia - Psicóloga Amanda Amarante</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>15 melhores Psicólogos de Curitiba para você e sua família.O Dr. Pedro Elias Sater atende na clínica...</t>
+          <t>Mande WhatsApp (clique) Ligue: (41) 98484-0002 doctoralia psicologo curitiba Agende pelo Doctoralia....</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1581,24 +1581,28 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.psicanaliseclinica.com/psicologos-de-curitiba/</t>
+          <t>https://www.psicologaamandaamarante.com.br/blog-psicologia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(CU) 98877-6655</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(41) 98484-0002</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5541984840002</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/20%20melhores%20Psicanalistas%20e%20Psiclogos%20de%20Curi%20curitiba</t>
+          <t>https://www.google.com/maps/search/Blog%20de%20Psicologia%20curitiba</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da 20 melhores Psicanalistas e Psiclogos de Curi aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Blog de Psicologia aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1608,29 +1612,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a 20 melhores Psicanalistas e Psiclogos de Curi?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Blog de Psicologia?</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%2020%20melhores%20Psicanalistas%20e%20Psiclogos%20de%20Curi%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541984840002?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Blog%20de%20Psicologia%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%2020%20melhores%20Psicanalistas%20e%20Psiclogos%20de%20Curi%3F</t>
+          <t>https://wa.me/5541984840002?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Blog%20de%20Psicologia%3F</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Rael Psiclogo</t>
+          <t>Terapia: como funciona e por que fazer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Rael Psicólogo - Curitiba Centro PR - Telefone... | Bendito Guia</t>
+          <t>Terapia: como funciona e por que fazer</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1645,7 +1649,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Encontre o telefone, endereço e whatsapp de Rael Psicólogo - Curitiba Centro PR em Atibaia. Veja ava...</t>
+          <t>WHATSAPP. paciente consultando psicologo. Terapia: como funciona, por que fazer e qual psicóloga esc...</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1655,28 +1659,28 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.benditoguia.com.br/empresa/rael-psicologo-curitiba-centro-pr</t>
+          <t>https://www.clinicaparanaense.com.br/como-funciona-terapia-psicologo-curitiba</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(41) 99600-4058</t>
+          <t>(41) 3021-6230</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5541996004058</t>
+          <t>554130216230</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Rael%20Psiclogo%20curitiba</t>
+          <t>https://www.google.com/maps/search/Terapia%3A%20como%20funciona%20e%20por%20que%20fazer%20curitiba</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Rael Psiclogo aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Terapia: como funciona e por que fazer aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1686,29 +1690,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Rael Psiclogo?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Terapia: como funciona e por que fazer?</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>https://wa.me/5541996004058?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Rael%20Psiclogo%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/554130216230?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Terapia%3A%20como%20funciona%20e%20por%20que%20fazer%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>https://wa.me/5541996004058?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Rael%20Psiclogo%3F</t>
+          <t>https://wa.me/554130216230?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Terapia%3A%20como%20funciona%20e%20por%20que%20fazer%3F</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>63 avaliaes sobre Clnica</t>
+          <t>20 melhores Psicanalistas e Psiclogos de Curi</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>63 avaliações sobre Clínica em Curitiba - Clínica Reintegrar...</t>
+          <t>20 melhores Psicanalistas e Psicólogos de Curitiba - Psicanálise.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1723,7 +1727,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Avaliações » Psicologo » Paraná » Curitiba » Clinica reintegrar.Mapa. Horário de funcionamento de Cl...</t>
+          <t>15 melhores Psicólogos de Curitiba para você e sua família.O Dr. Pedro Elias Sater atende na clínica...</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1733,7 +1737,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://avaliacoesbrasil.com/psicologo/curitiba/clinica-reintegrar/</t>
+          <t>https://www.psicanaliseclinica.com/psicologos-de-curitiba/</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1744,13 +1748,13 @@
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/63%20avaliaes%20sobre%20Clnica%20curitiba</t>
+          <t>https://www.google.com/maps/search/20%20melhores%20Psicanalistas%20e%20Psiclogos%20de%20Curi%20curitiba</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da 63 avaliaes sobre Clnica aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da 20 melhores Psicanalistas e Psiclogos de Curi aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1760,29 +1764,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a 63 avaliaes sobre Clnica?</t>
+Posso te mandar a prévia demonstrativa que fiz para a 20 melhores Psicanalistas e Psiclogos de Curi?</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%2063%20avaliaes%20sobre%20Clnica%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%2020%20melhores%20Psicanalistas%20e%20Psiclogos%20de%20Curi%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%2063%20avaliaes%20sobre%20Clnica%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%2020%20melhores%20Psicanalistas%20e%20Psiclogos%20de%20Curi%3F</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Psiclogo Gratuito</t>
+          <t>Rael Psiclogo</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Psicólogo Gratuito em Curitiba - Psicólogo gratuito, Psicólogo...</t>
+          <t>Rael Psicólogo - Curitiba Centro PR - Telefone... | Bendito Guia</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1797,7 +1801,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Psicólogo Gratuito em Curitiba. Buscar apoio psicológico é um passo importante para o bem-estar.Tele...</t>
+          <t>Encontre o telefone, endereço e whatsapp de Rael Psicólogo - Curitiba Centro PR em Atibaia. Veja ava...</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1807,28 +1811,28 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://psicologogratuito.com.br/psicologo-gratuito-em-curitiba/</t>
+          <t>https://www.benditoguia.com.br/empresa/rael-psicologo-curitiba-centro-pr</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(41) 3310-1515</t>
+          <t>(41) 99600-4058</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>554133101515</t>
+          <t>5541996004058</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Psiclogo%20Gratuito%20curitiba</t>
+          <t>https://www.google.com/maps/search/Rael%20Psiclogo%20curitiba</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Psiclogo Gratuito aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Rael Psiclogo aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1838,29 +1842,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Psiclogo Gratuito?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Rael Psiclogo?</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>https://wa.me/554133101515?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Psiclogo%20Gratuito%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541996004058?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Rael%20Psiclogo%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>https://wa.me/554133101515?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Psiclogo%20Gratuito%3F</t>
+          <t>https://wa.me/5541996004058?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Rael%20Psiclogo%3F</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sabina Arajo Dos Santos Fagundes, Psiclogo</t>
+          <t>Terapia presencial</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sabina Araújo Dos Santos Fagundes, Psicólogo em Curitiba - PR</t>
+          <t>Terapia presencial em Curitiba - Psicologo Rafael Freire</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1875,7 +1879,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Terapia Comportamental. Transtornos em Crianças e Adolescentes. Psicopedagogia Clinica. Altas Habili...</t>
+          <t>Faça Terapia presencial em Curitiba. Com comodidade, sigilo e segurança, posso ajudar você a ser sua...</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1885,7 +1889,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://agenda.app.br/especialista/sabina-araujo-dos-santos-fagundes-psicologo-curitiba-pr</t>
+          <t>https://psirafaelfreire.com.br/</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1896,13 +1900,13 @@
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Sabina%20Arajo%20Dos%20Santos%20Fagundes%2C%20Psiclogo%20curitiba</t>
+          <t>https://www.google.com/maps/search/Terapia%20presencial%20curitiba</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Sabina Arajo Dos Santos Fagundes, Psiclogo aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Terapia presencial aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1912,29 +1916,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Sabina Arajo Dos Santos Fagundes, Psiclogo?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Terapia presencial?</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Sabina%20Arajo%20Dos%20Santos%20Fagundes%2C%20Psiclogo%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Terapia%20presencial%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Sabina%20Arajo%20Dos%20Santos%20Fagundes%2C%20Psiclogo%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Terapia%20presencial%3F</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Clnica de Psicologia</t>
+          <t>Psicloga</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Clínica de Psicologia em Curitiba PR | Clínica EOS</t>
+          <t>Psicóloga em Curitiba | Elisiane Siqueira - TCC e Terapia Online</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1949,7 +1953,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Entre em contato conosco por telefone, e-mail ou através do nosso site para marcar sua consulta. Est...</t>
+          <t>Psicóloga clínica com 30+ anos. Especialista em TCC e Terapia do Esquema. Atendimento no Cabral e on...</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1959,24 +1963,28 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://clinicapsieos.com.br/</t>
+          <t>https://www.elisianesiqueira.com.br/</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(CU) 98877-6655</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(11) 98723-2712</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>5511987232712</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Clnica%20de%20Psicologia%20curitiba</t>
+          <t>https://www.google.com/maps/search/Psicloga%20curitiba</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Clnica de Psicologia aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Psicloga aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1986,29 +1994,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Clnica de Psicologia?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Psicloga?</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Clnica%20de%20Psicologia%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5511987232712?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Psicloga%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Clnica%20de%20Psicologia%3F</t>
+          <t>https://wa.me/5511987232712?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Psicloga%3F</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Clnica Centro Do Ser / Psicologia / Curitiba</t>
+          <t>Clnica de Psicologia</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Clínica Centro Do Ser / Psicologia / Curitiba</t>
+          <t>Clínica de Psicologia em Curitiba PR | Clínica EOS</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2023,7 +2031,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>A Clínica Centro do Ser oferece instalações modernas e profissionais de saúde experientes e dedicado...</t>
+          <t>Clínica de psicologia em Curitiba PR, oferecendo atendimento psicológico de qualidade. Agende sua co...</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2033,28 +2041,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.centrodoser.com.br/</t>
+          <t>https://clinicapsieos.com.br/</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(41) 98516-5591</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>5541985165591</t>
-        </is>
-      </c>
+          <t>(CU) 98877-6655</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Clnica%20Centro%20Do%20Ser%20/%20Psicologia%20/%20Curitiba%20curitiba</t>
+          <t>https://www.google.com/maps/search/Clnica%20de%20Psicologia%20curitiba</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Clnica Centro Do Ser / Psicologia / Curitiba aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Clnica de Psicologia aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2064,29 +2068,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Clnica Centro Do Ser / Psicologia / Curitiba?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Clnica de Psicologia?</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>https://wa.me/5541985165591?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Clnica%20Centro%20Do%20Ser%20/%20Psicologia%20/%20Curitiba%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Clnica%20de%20Psicologia%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>https://wa.me/5541985165591?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Clnica%20Centro%20Do%20Ser%20/%20Psicologia%20/%20Curitiba%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Clnica%20de%20Psicologia%3F</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Tele</t>
+          <t>Hudson Padilha • Psiclogo Curitiba. Psicanali</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Teleconsulta com Psicólogo em Curitiba - PR na Plataforma de...</t>
+          <t>Hudson Padilha • Psicólogo Curitiba. Psicanalista ...</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2101,7 +2105,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Agende a sua teleconsulta com Psicólogo na Telemedicina Morsch. Escolha o profissional, dia e horári...</t>
+          <t>Psicólogo com mais de 15 anos de experiência realizando atendimentos presenciais em Curitiba e onlin...</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2111,7 +2115,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://telemedicinamorsch.com.br/especialidade/psicologo/curitiba-pr</t>
+          <t>https://www.hudsonpadilha.com/</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2122,13 +2126,13 @@
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Tele%20curitiba</t>
+          <t>https://www.google.com/maps/search/Hudson%20Padilha%20%E2%80%A2%20Psiclogo%20Curitiba.%20Psicanali%20curitiba</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Tele aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Hudson Padilha • Psiclogo Curitiba. Psicanali aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2138,29 +2142,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Tele?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Hudson Padilha • Psiclogo Curitiba. Psicanali?</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Tele%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Hudson%20Padilha%20%E2%80%A2%20Psiclogo%20Curitiba.%20Psicanali%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Tele%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Hudson%20Padilha%20%E2%80%A2%20Psiclogo%20Curitiba.%20Psicanali%3F</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Psicologia e Psiquiatria</t>
+          <t>Consulte com um psiclogo online de qualquer l</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Psicologia e Psiquiatria | Curitiba | Clínica Protheus</t>
+          <t>Consulte com um psicólogo online de qualquer lugar - Psicologia V</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2175,7 +2179,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>A Clínica Protheus é um espaço de promoção da Saúde Mental que atende crianças, jovens e adultos nas...</t>
+          <t>Norton de S. - Psicólogo. "Sinceramente, estou surpreso com tanto carinho e agilidade desta platafor...</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2185,7 +2189,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.clinicaprotheus.com.br/</t>
+          <t>https://www.psicologiaviva.com.br/</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2196,13 +2200,13 @@
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Psicologia%20e%20Psiquiatria%20curitiba</t>
+          <t>https://www.google.com/maps/search/Consulte%20com%20um%20psiclogo%20online%20de%20qualquer%20l%20curitiba</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Psicologia e Psiquiatria aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Consulte com um psiclogo online de qualquer l aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2212,29 +2216,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Psicologia e Psiquiatria?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Consulte com um psiclogo online de qualquer l?</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Psicologia%20e%20Psiquiatria%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Consulte%20com%20um%20psiclogo%20online%20de%20qualquer%20l%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Psicologia%20e%20Psiquiatria%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Consulte%20com%20um%20psiclogo%20online%20de%20qualquer%20l%3F</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Psicologo Curitiba</t>
+          <t>Terapia online com psiclogos disponveis 24h p</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Psicologo Curitiba - Guilherme Moro | HelpSaúde</t>
+          <t>Terapia online com psicólogos disponíveis 24h por dia | Zenklub</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2249,38 +2253,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Você já se consultou com Psicologo Curitiba - Guilherme Moro? Conte aqui como foi. Outros pacientes ...</t>
+          <t>Estamos sempre com você. Todo dia e a qualquer hora, nossos especialistas estarão disponíveis para a...</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>SITE FORA DO AR / LINK QUEBRADO 🚨</t>
+          <t>SITE ATIVO 📱</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.helpsaude.com/guilherme-moro.psicologo.pr0816488</t>
+          <t>https://zenklub.com.br/</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(41) 9644-0186</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>554196440186</t>
-        </is>
-      </c>
+          <t>(CU) 98877-6655</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Psicologo%20Curitiba%20curitiba</t>
+          <t>https://www.google.com/maps/search/Terapia%20online%20com%20psiclogos%20disponveis%2024h%20p%20curitiba</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Psicologo Curitiba aí em Curitiba no Google e fui tentar acessar o site de vocês e vi que está fora do ar.
+Vi o perfil da Terapia online com psiclogos disponveis 24h p aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2290,29 +2290,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Psicologo Curitiba?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Terapia online com psiclogos disponveis 24h p?</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>https://wa.me/554196440186?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Psicologo%20Curitiba%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20fui%20tentar%20acessar%20o%20site%20de%20voc%C3%AAs%20e%20vi%20que%20est%C3%A1%20fora%20do%20ar.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Terapia%20online%20com%20psiclogos%20disponveis%2024h%20p%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>https://wa.me/554196440186?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Psicologo%20Curitiba%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Terapia%20online%20com%20psiclogos%20disponveis%2024h%20p%3F</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Vagas de Psicologia</t>
+          <t>Fala.BR</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Vagas de Psicologia em Curitiba, PR | Indeed</t>
+          <t>Fala.BR - Plataforma Integrada de Ouvidoria e Acesso à Informação</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Instituição de Saúde e Reabilitação busca profissional Psicólogo em Curitiba (Rebouças). Realizar at...</t>
+          <t>Entrar em Contato Entre em contato com a ouvidoria, cadastrando sua......</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2337,24 +2337,28 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://br.indeed.com/q-psicologia-l-curitiba,-pr-vagas.html</t>
+          <t>https://falabr.cgu.gov.br/</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(CU) 98877-6655</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(41) 3350-8484</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>554133508484</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Vagas%20de%20Psicologia%20curitiba</t>
+          <t>https://www.google.com/maps/search/Fala.BR%20curitiba</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Vagas de Psicologia aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Fala.BR aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2364,29 +2368,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Vagas de Psicologia?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Fala.BR?</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Vagas%20de%20Psicologia%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/554133508484?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Fala.BR%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Vagas%20de%20Psicologia%3F</t>
+          <t>https://wa.me/554133508484?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Fala.BR%3F</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Andre Valente</t>
+          <t>Portal</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Andre Valente - Psicólogo Clínico na Fundação Estatal de... | Lin</t>
+          <t>Portal - Detran-SP</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2401,7 +2405,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Psicólogo Residente. Hospital de Clínicas UFPR. fev. de 2013 - mar. de 2015 2 anos 2 meses. Curitiba...</t>
+          <t>O novo Portal do Detran-SP feito pra você! Mais fácil, rápido e digital. Pra você não perder tempo c...</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2411,28 +2415,28 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://br.linkedin.com/in/andre-valente-93281913a</t>
+          <t>https://www.detran.sp.gov.br/</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(19) 0745-0980</t>
+          <t>(41) 3019-2000</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>551907450980</t>
+          <t>554130192000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Andre%20Valente%20curitiba</t>
+          <t>https://www.google.com/maps/search/Portal%20curitiba</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Andre Valente aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Portal aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2442,29 +2446,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Andre Valente?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Portal?</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>https://wa.me/551907450980?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Andre%20Valente%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/554130192000?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Portal%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>https://wa.me/551907450980?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Andre%20Valente%3F</t>
+          <t>https://wa.me/554130192000?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Portal%3F</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Terapia online com psiclogos disponveis 24h p</t>
+          <t>Web site created using create-react-app</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Terapia online com psicólogos disponíveis 24h por dia | Zenklub</t>
+          <t>Web site created using create-react-app</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2479,17 +2483,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Estamos sempre com você. Todo dia e a qualquer hora, nossos especialistas estarão disponíveis para a...</t>
+          <t>Web site created using create-react-app......</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>SITE ATIVO 📱</t>
+          <t>SITE FORA DO AR / LINK QUEBRADO 🚨</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://zenklub.com.br/</t>
+          <t>https://cadunico.dataprev.gov.br/</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2500,13 +2504,13 @@
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Terapia%20online%20com%20psiclogos%20disponveis%2024h%20p%20curitiba</t>
+          <t>https://www.google.com/maps/search/Web%20site%20created%20using%20create-react-app%20curitiba</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Terapia online com psiclogos disponveis 24h p aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Web site created using create-react-app aí em Curitiba no Google e fui tentar acessar o site de vocês e vi que está fora do ar.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2516,29 +2520,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Terapia online com psiclogos disponveis 24h p?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Web site created using create-react-app?</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Terapia%20online%20com%20psiclogos%20disponveis%2024h%20p%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Web%20site%20created%20using%20create-react-app%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20fui%20tentar%20acessar%20o%20site%20de%20voc%C3%AAs%20e%20vi%20que%20est%C3%A1%20fora%20do%20ar.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Terapia%20online%20com%20psiclogos%20disponveis%2024h%20p%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Web%20site%20created%20using%20create-react-app%3F</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Web site created using create-react-app</t>
+          <t>Barbearia</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Web site created using create-react-app</t>
+          <t>Barbearia em Curitiba - perto de mim - Cabeleireiro masculino ...</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2553,34 +2557,38 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Web site created using create-react-app......</t>
+          <t>Um recurso incrível que você pode utilizar é o nosso mapa virtual, em que você pode encontrar todas ...</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>SITE FORA DO AR / LINK QUEBRADO 🚨</t>
+          <t>SITE ATIVO 📱</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://cadunico.dataprev.gov.br/</t>
+          <t>https://booksy.com/pt-br/s/barbearias/583853_curitiba</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(CU) 98877-6655</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(41) 99861-8127</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5541998618127</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Web%20site%20created%20using%20create-react-app%20curitiba</t>
+          <t>https://www.google.com/maps/search/Barbearia%20curitiba</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Web site created using create-react-app aí em Curitiba no Google e fui tentar acessar o site de vocês e vi que está fora do ar.
+Vi o perfil da Barbearia aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2590,29 +2598,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Web site created using create-react-app?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Barbearia?</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Web%20site%20created%20using%20create-react-app%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20fui%20tentar%20acessar%20o%20site%20de%20voc%C3%AAs%20e%20vi%20que%20est%C3%A1%20fora%20do%20ar.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541998618127?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Barbearia%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Web%20site%20created%20using%20create-react-app%3F</t>
+          <t>https://wa.me/5541998618127?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Barbearia%3F</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Portal</t>
+          <t>Os melhores barbeiros perto de mim</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Portal - Detran-SP</t>
+          <t>Os melhores barbeiros perto de mim em Curitiba - Fresha</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2627,7 +2635,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>O novo Portal do Detran-SP feito pra você! Mais fácil, rápido e digital. Pra você não perder tempo c...</t>
+          <t>Agendar online com os melhores Barbeiros perto de você em Curitiba. Excelentes ofertas e descontos! ...</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2637,7 +2645,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.detran.sp.gov.br/</t>
+          <t>https://www.fresha.com/lp/pt/bt/barbearias/br-curitiba</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2648,13 +2656,13 @@
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Portal%20curitiba</t>
+          <t>https://www.google.com/maps/search/Os%20melhores%20barbeiros%20perto%20de%20mim%20curitiba</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Portal aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Os melhores barbeiros perto de mim aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2664,29 +2672,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Portal?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Os melhores barbeiros perto de mim?</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Portal%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Os%20melhores%20barbeiros%20perto%20de%20mim%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Portal%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Os%20melhores%20barbeiros%20perto%20de%20mim%3F</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Barbearia</t>
+          <t>15 Melhores Barbearias no Porto</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Barbearia em Curitiba - perto de mim - Cabeleireiro masculino ...</t>
+          <t>15 Melhores Barbearias no Portão em Curitiba — Guia 2026</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2701,7 +2709,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Um recurso incrível que você pode utilizar é o nosso mapa virtual, em que você pode encontrar todas ...</t>
+          <t>Seja para um corte moderno ou uma barba clássica, você encontra ótimas opções por aqui. Neste guia r...</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2711,28 +2719,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://booksy.com/pt-br/s/barbearias/583853_curitiba</t>
+          <t>https://blog.beard.com.br/barbearias-no-portao-curitiba/</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(41) 3501-0365</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>554135010365</t>
-        </is>
-      </c>
+          <t>(CU) 98877-6655</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Barbearia%20curitiba</t>
+          <t>https://www.google.com/maps/search/15%20Melhores%20Barbearias%20no%20Porto%20curitiba</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Barbearia aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da 15 Melhores Barbearias no Porto aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2742,29 +2746,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Barbearia?</t>
+Posso te mandar a prévia demonstrativa que fiz para a 15 Melhores Barbearias no Porto?</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>https://wa.me/554135010365?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Barbearia%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%2015%20Melhores%20Barbearias%20no%20Porto%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>https://wa.me/554135010365?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Barbearia%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%2015%20Melhores%20Barbearias%20no%20Porto%3F</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Os melhores barbeiros perto de mim</t>
+          <t>barbearias</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Os melhores barbeiros perto de mim em Curitiba - FreshaBarbearia </t>
+          <t>barbearias em Curitiba 2026 | OndeAbrir</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2779,7 +2783,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Agendar online com os melhores Barbeiros perto de você em Curitiba. Excelentes ofertas e descontos! ...</t>
+          <t>Panorama competitivo: barbearias em Curitiba. Curitiba tem 1.8M habitantes e um mercado de barbearia...</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2789,7 +2793,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.fresha.com/lp/pt/bt/barbearias/br-curitiba</t>
+          <t>https://ondeabrir.com/mercado/barbearia/curitiba</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2800,13 +2804,13 @@
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Os%20melhores%20barbeiros%20perto%20de%20mim%20curitiba</t>
+          <t>https://www.google.com/maps/search/barbearias%20curitiba</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Os melhores barbeiros perto de mim aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da barbearias aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2816,29 +2820,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Os melhores barbeiros perto de mim?</t>
+Posso te mandar a prévia demonstrativa que fiz para a barbearias?</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Os%20melhores%20barbeiros%20perto%20de%20mim%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20barbearias%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Os%20melhores%20barbeiros%20perto%20de%20mim%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20barbearias%3F</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Barbearia Saint Germain</t>
+          <t>Barbers In Barbearia</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Barbearia Saint Germain | Curitiba</t>
+          <t>Barbers In Barbearia - Curitiba - Faça Agendamentos Online - Preç</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2853,7 +2857,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Para quem busca uma barbearia em Curitiba que combine sofisticação, qualidade e atendimento atencios...</t>
+          <t>Confira Barbers In Barbearia em Curitiba - explore preços, avaliações e faça agendamentos online 24 ...</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2863,28 +2867,28 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.barbeariasg.com/</t>
+          <t>https://booksy.com/pt-br/99716_barbers-in-barbearia_barbearias_583853_curitiba</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(41) 99894-4124</t>
+          <t>(41) 3598-9540</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>5541998944124</t>
+          <t>554135989540</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Barbearia%20Saint%20Germain%20curitiba</t>
+          <t>https://www.google.com/maps/search/Barbers%20In%20Barbearia%20curitiba</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Barbearia Saint Germain aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Barbers In Barbearia aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2894,29 +2898,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Barbearia Saint Germain?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Barbers In Barbearia?</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>https://wa.me/5541998944124?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Barbearia%20Saint%20Germain%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/554135989540?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Barbers%20In%20Barbearia%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>https://wa.me/5541998944124?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Barbearia%20Saint%20Germain%3F</t>
+          <t>https://wa.me/554135989540?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Barbers%20In%20Barbearia%3F</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>15 Melhores Barbearias no Rebouas</t>
+          <t>Melhores Servios de Barbearias</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>15 Melhores Barbearias no Rebouças em Curitiba — Guia 2026</t>
+          <t>Melhores Serviços de Barbearias em Curitiba, PR | GuiaFix</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2931,7 +2935,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Neste guia reunimos as 15 melhores barbearias no Rebouças, selecionadas com base nas avaliações reai...</t>
+          <t>Descubra a Soul Barbearia, localizada no Shopping Estação de Curitiba. Nossa barbearia oferece um am...</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2941,7 +2945,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://blog.beard.com.br/barbearias-no-reboucas-curitiba/</t>
+          <t>https://guiafix.com.br/curitiba-pr/barbearias</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2952,13 +2956,13 @@
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/15%20Melhores%20Barbearias%20no%20Rebouas%20curitiba</t>
+          <t>https://www.google.com/maps/search/Melhores%20Servios%20de%20Barbearias%20curitiba</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da 15 Melhores Barbearias no Rebouas aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Melhores Servios de Barbearias aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2968,29 +2972,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a 15 Melhores Barbearias no Rebouas?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Melhores Servios de Barbearias?</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%2015%20Melhores%20Barbearias%20no%20Rebouas%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Melhores%20Servios%20de%20Barbearias%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%2015%20Melhores%20Barbearias%20no%20Rebouas%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Melhores%20Servios%20de%20Barbearias%3F</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>barbearias</t>
+          <t>Barbearia Clube</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>barbearias em Curitiba 2026 | OndeAbrir</t>
+          <t>Barbearia Clube | Tradição e Excelência em Curitiba (Mercês)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3005,7 +3009,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Panorama competitivo: barbearias em Curitiba. Curitiba tem 1.8M habitantes e um mercado de barbearia...</t>
+          <t>A barbearia clássica preferida de Curitiba. Barbearia Clube: Barba na navalha, cortes visagistas, Di...</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -3015,24 +3019,28 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://ondeabrir.com/mercado/barbearia/curitiba</t>
+          <t>https://barbeariaclube.com.br/</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(CU) 98877-6655</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(41) 3014-9413</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>554130149413</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/barbearias%20curitiba</t>
+          <t>https://www.google.com/maps/search/Barbearia%20Clube%20curitiba</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da barbearias aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Barbearia Clube aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -3042,29 +3050,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a barbearias?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Barbearia Clube?</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20barbearias%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/554130149413?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Barbearia%20Clube%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20barbearias%3F</t>
+          <t>https://wa.me/554130149413?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Barbearia%20Clube%3F</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Barbers In Barbearia</t>
+          <t>AutoRank para Barbearias</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Barbers In Barbearia - Curitiba - Faça Agendamentos Online - Preç</t>
+          <t>AutoRank para Barbearias em Curitiba | Seu Negócio na Primeira...</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3079,7 +3087,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Confira Barbers In Barbearia em Curitiba - explore preços, avaliações e faça agendamentos online 24 ...</t>
+          <t>Barbearias em Curitiba. Coloque sua barbearia na primeira página do Google e atraia clientes buscand...</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3089,28 +3097,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://booksy.com/pt-br/99716_barbers-in-barbearia_barbearias_583853_curitiba</t>
+          <t>https://www.autorank.com.br/barbearia/curitiba</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(41) 3598-9540</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>554135989540</t>
-        </is>
-      </c>
+          <t>(CU) 98877-6655</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Barbers%20In%20Barbearia%20curitiba</t>
+          <t>https://www.google.com/maps/search/AutoRank%20para%20Barbearias%20curitiba</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Barbers In Barbearia aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da AutoRank para Barbearias aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -3120,29 +3124,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Barbers In Barbearia?</t>
+Posso te mandar a prévia demonstrativa que fiz para a AutoRank para Barbearias?</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>https://wa.me/554135989540?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Barbers%20In%20Barbearia%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20AutoRank%20para%20Barbearias%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>https://wa.me/554135989540?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Barbers%20In%20Barbearia%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20AutoRank%20para%20Barbearias%3F</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Melhores Servios de Barbearias</t>
+          <t>Barbearia John Six</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Melhores Serviços de Barbearias em Curitiba, PR | GuiaFix</t>
+          <t>Barbearia John Six - Bigorrilho em Curitiba - PR | Locais do Bras</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3157,7 +3161,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Descubra a Soul Barbearia, localizada no Shopping Estação de Curitiba. Nossa barbearia oferece um am...</t>
+          <t>Barbearia John Six - Bigorrilho atua no ramo de Barbearia, horário de funcionamento quarta a quinta-...</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3167,24 +3171,28 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://guiafix.com.br/curitiba-pr/barbearias</t>
+          <t>https://www.locaisdobrasil.com.br/encontre/barbearia/curitiba-pr/barbearia-john-six-bigorrilho/61cf4338c76c53fe0914d004</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(CU) 98877-6655</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(41) 99553-7410</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>5541995537410</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Melhores%20Servios%20de%20Barbearias%20curitiba</t>
+          <t>https://www.google.com/maps/search/Barbearia%20John%20Six%20curitiba</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Melhores Servios de Barbearias aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Barbearia John Six aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -3194,29 +3202,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Melhores Servios de Barbearias?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Barbearia John Six?</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Melhores%20Servios%20de%20Barbearias%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541995537410?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Barbearia%20John%20Six%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Melhores%20Servios%20de%20Barbearias%3F</t>
+          <t>https://wa.me/5541995537410?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Barbearia%20John%20Six%3F</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Barbearia Clube</t>
+          <t>Shelby Barbearia</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Barbearia Clube | Tradição e Excelência em Curitiba (Mercês)</t>
+          <t>Shelby Barbearia - (41) 98475-3472 BARBEARIA EM CURITIBA...</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3231,7 +3239,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>A barbearia clássica preferida de Curitiba. Barbearia Clube: Barba na navalha, cortes visagistas, Di...</t>
+          <t>Há 6 anos, a Shelby Barbearia vem construindo uma história de dedicação, estilo e excelência em Curi...</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3241,28 +3249,28 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://barbeariaclube.com.br/</t>
+          <t>https://barbeariashelby.com.br/sobre-nos/</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(41) 3014-9413</t>
+          <t>(41) 98475-3472</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>554130149413</t>
+          <t>5541984753472</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Barbearia%20Clube%20curitiba</t>
+          <t>https://www.google.com/maps/search/Shelby%20Barbearia%20curitiba</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Barbearia Clube aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Shelby Barbearia aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -3272,469 +3280,17 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Barbearia Clube?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Shelby Barbearia?</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>https://wa.me/554130149413?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Barbearia%20Clube%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541984753472?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Shelby%20Barbearia%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>https://wa.me/554130149413?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Barbearia%20Clube%3F</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>AutoRank para Barbearias</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>AutoRank para Barbearias em Curitiba | Seu Negócio na Primeira...</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Curitiba</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Centro / Região</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Barbearias em Curitiba. Coloque sua barbearia na primeira página do Google e atraia clientes buscand...</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>SITE ATIVO 📱</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://www.autorank.com.br/barbearia/curitiba</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>(CU) 98877-6655</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/AutoRank%20para%20Barbearias%20curitiba</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da AutoRank para Barbearias aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
-Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
-Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
-A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
-Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a AutoRank para Barbearias?</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20AutoRank%20para%20Barbearias%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20AutoRank%20para%20Barbearias%3F</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Shelby Barbearia</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Shelby Barbearia - (41) 98475-3472 BARBEARIA EM CURITIBA...</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Curitiba</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Centro / Região</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Há 6 anos, a Shelby Barbearia vem construindo uma história de dedicação, estilo e excelência em Curi...</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>SITE ATIVO 📱</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://barbeariashelby.com.br/sobre-nos/</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>(41) 98475-3472</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>5541984753472</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/Shelby%20Barbearia%20curitiba</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Shelby Barbearia aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
-Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
-Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
-A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
-Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Shelby Barbearia?</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>https://wa.me/5541984753472?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Shelby%20Barbearia%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
           <t>https://wa.me/5541984753472?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Shelby%20Barbearia%3F</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Barbearia John Six</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Barbearia John Six - Bigorrilho em Curitiba - PR | Locais do Bras</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Curitiba</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Centro / Região</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Barbearia John Six - Bigorrilho atua no ramo de Barbearia, horário de funcionamento quarta a quinta-...</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>SITE ATIVO 📱</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>https://www.locaisdobrasil.com.br/encontre/barbearia/curitiba-pr/barbearia-john-six-bigorrilho/61cf4338c76c53fe0914d004</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(41) 99553-7410</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>5541995537410</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/Barbearia%20John%20Six%20curitiba</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Barbearia John Six aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
-Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
-Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
-A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
-Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Barbearia John Six?</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>https://wa.me/5541995537410?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Barbearia%20John%20Six%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>https://wa.me/5541995537410?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Barbearia%20John%20Six%3F</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>CNPJ 53.441.822/0001-74</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>CNPJ 53.441.822/0001-74 - barbearia curitiba ltda | CNPJ go!</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Curitiba</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Centro / Região</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Enriqueça empresas com Google Maps, Instagram, LinkedIn e mais. A IA gera pitchs personalizados para...</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>SITE ATIVO 📱</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>https://cnpjgo.com.br/cnpj/53441822000174</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>(CU) 98877-6655</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/CNPJ%2053.441.822/0001-74%20curitiba</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da CNPJ 53.441.822/0001-74 aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
-Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
-Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
-A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
-Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a CNPJ 53.441.822/0001-74?</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20CNPJ%2053.441.822/0001-74%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20CNPJ%2053.441.822/0001-74%3F</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Victor Hugo Barbeiro da Lenno Barbearia</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Victor Hugo Barbeiro da Lenno Barbearia - Curitiba 2017 - YouTube</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Curitiba</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Centro / Região</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>© 2025 Google LLC....</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>SEM SITE PRÓPRIO (OPORTUNIDADE 🔥)</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Sem Site Cadastrado</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(CU) 98877-6655</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/Victor%20Hugo%20Barbeiro%20da%20Lenno%20Barbearia%20curitiba</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Victor Hugo Barbeiro da Lenno Barbearia aí em Curitiba no Google e vi que vocês ainda não têm um site próprio para celular.
-Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
-Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
-A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
-Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Victor Hugo Barbeiro da Lenno Barbearia?</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Victor%20Hugo%20Barbeiro%20da%20Lenno%20Barbearia%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20voc%C3%AAs%20ainda%20n%C3%A3o%20t%C3%AAm%20um%20site%20pr%C3%B3prio%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Victor%20Hugo%20Barbeiro%20da%20Lenno%20Barbearia%3F</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Link to instagram.com</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Link to instagram.com</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Curitiba</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Centro / Região</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>The site owner hides the web page description....</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>SEM SITE PRÓPRIO (OPORTUNIDADE 🔥)</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Sem Site Cadastrado</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>(CU) 98877-6655</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/Link%20to%20instagram.com%20curitiba</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Link to instagram.com aí em Curitiba no Google e vi que vocês ainda não têm um site próprio para celular.
-Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
-Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
-A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
-Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Link to instagram.com?</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Link%20to%20instagram.com%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20voc%C3%AAs%20ainda%20n%C3%A3o%20t%C3%AAm%20um%20site%20pr%C3%B3prio%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Link%20to%20instagram.com%3F</t>
         </is>
       </c>
     </row>

--- a/leads_psicologo_curitiba.xlsx
+++ b/leads_psicologo_curitiba.xlsx
@@ -491,7 +491,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Psicloga online / Psicloga Curitiba</t>
+          <t>Psicloga Online</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,7 +565,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AutoRank para Psiclogos</t>
+          <t>Autorank para Psiclogos</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -639,7 +639,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>10 melhores psiclogos para Curitiba</t>
+          <t>10 Melhores Psiclogos para</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -677,10 +677,8 @@
           <t>(41) 99953-9370</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5541999539370</t>
-        </is>
+      <c r="I4" t="n">
+        <v>5541999539370</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -717,7 +715,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Em busca de um psiclogo</t>
+          <t>Em Busca de Um Psiclogo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -791,7 +789,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20 psiclogos</t>
+          <t>20 Psiclogos</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -865,7 +863,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Psiclogos Curitiba</t>
+          <t>Psiclogos</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -977,10 +975,8 @@
           <t>(41) 9219-2223</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>554192192223</t>
-        </is>
+      <c r="I8" t="n">
+        <v>554192192223</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1017,7 +1013,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Link to facebook.com</t>
+          <t>Link To Facebook.com</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1129,10 +1125,8 @@
           <t>(41) 98484-0002</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5541984840002</t>
-        </is>
+      <c r="I10" t="n">
+        <v>5541984840002</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1207,10 +1201,8 @@
           <t>(41) 3248-4551</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>554132484551</t>
-        </is>
+      <c r="I11" t="n">
+        <v>554132484551</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1247,7 +1239,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Psiclogo, Curitiba, PR</t>
+          <t>Psiclogo</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1321,7 +1313,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Salrio: Psicologo</t>
+          <t>Salrio</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1395,7 +1387,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Psiclogos, Clnicas de Psicologia na Cidade de</t>
+          <t>Psiclogos, Clnicas de Psicologia Na Cida</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1433,10 +1425,8 @@
           <t>(41) 3223-8630</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>554132238630</t>
-        </is>
+      <c r="I14" t="n">
+        <v>554132238630</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1511,10 +1501,8 @@
           <t>(41) 99866-3402</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>5541998663402</t>
-        </is>
+      <c r="I15" t="n">
+        <v>5541998663402</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1589,10 +1577,8 @@
           <t>(41) 98484-0002</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>5541984840002</t>
-        </is>
+      <c r="I16" t="n">
+        <v>5541984840002</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1629,14 +1615,14 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>Terapia: Como Funciona e por Que Fazer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>Terapia: como funciona e por que fazer</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Terapia: como funciona e por que fazer</t>
-        </is>
-      </c>
       <c r="C17" t="inlineStr">
         <is>
           <t>Curitiba</t>
@@ -1667,10 +1653,8 @@
           <t>(41) 3021-6230</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>554130216230</t>
-        </is>
+      <c r="I17" t="n">
+        <v>554130216230</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1707,7 +1691,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20 melhores Psicanalistas e Psiclogos de Curi</t>
+          <t>20 Melhores Psicanalistas e Psiclogos de</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1819,10 +1803,8 @@
           <t>(41) 99600-4058</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>5541996004058</t>
-        </is>
+      <c r="I19" t="n">
+        <v>5541996004058</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1859,7 +1841,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Terapia presencial</t>
+          <t>Terapia Presencial</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1971,10 +1953,8 @@
           <t>(11) 98723-2712</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>5511987232712</t>
-        </is>
+      <c r="I21" t="n">
+        <v>5511987232712</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -2085,7 +2065,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Hudson Padilha • Psiclogo Curitiba. Psicanali</t>
+          <t>Hudson Padilha • Psiclogo Curitiba. Psic</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2159,7 +2139,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Consulte com um psiclogo online de qualquer l</t>
+          <t>Consulte com Um Psiclogo Online de Qualq</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2233,7 +2213,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Terapia online com psiclogos disponveis 24h p</t>
+          <t>Terapia Online com Psiclogos Disponveis</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2307,7 +2287,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Fala.BR</t>
+          <t>Fala.br</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2345,10 +2325,8 @@
           <t>(41) 3350-8484</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>554133508484</t>
-        </is>
+      <c r="I26" t="n">
+        <v>554133508484</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -2423,10 +2401,8 @@
           <t>(41) 3019-2000</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>554130192000</t>
-        </is>
+      <c r="I27" t="n">
+        <v>554130192000</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2463,7 +2439,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Web site created using create-react-app</t>
+          <t>Web Site Created Using Create-react-app</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2575,10 +2551,8 @@
           <t>(41) 99861-8127</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>5541998618127</t>
-        </is>
+      <c r="I29" t="n">
+        <v>5541998618127</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -2615,7 +2589,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Os melhores barbeiros perto de mim</t>
+          <t>Os Melhores Barbeiros Perto de Mim</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2689,7 +2663,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>15 Melhores Barbearias no Porto</t>
+          <t>15 Melhores Barbearias No Porto</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2763,7 +2737,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>barbearias</t>
+          <t>Barbearias</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2875,10 +2849,8 @@
           <t>(41) 3598-9540</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>554135989540</t>
-        </is>
+      <c r="I33" t="n">
+        <v>554135989540</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -3027,10 +2999,8 @@
           <t>(41) 3014-9413</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>554130149413</t>
-        </is>
+      <c r="I35" t="n">
+        <v>554130149413</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -3067,7 +3037,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AutoRank para Barbearias</t>
+          <t>Autorank para Barbearias</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3179,10 +3149,8 @@
           <t>(41) 99553-7410</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>5541995537410</t>
-        </is>
+      <c r="I37" t="n">
+        <v>5541995537410</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -3257,10 +3225,8 @@
           <t>(41) 98475-3472</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>5541984753472</t>
-        </is>
+      <c r="I38" t="n">
+        <v>5541984753472</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
